--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl.sharepoint.com/sites/Zib-transitiecommunity/Gedeelde documenten/Architectuur/Werkgroepen ZIBS 2.0 Implementatie/Bouwblokken/Condition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1612" documentId="8_{14C11024-DAA1-4BC8-A0C0-1702803526E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACD9D79-9A41-4C2C-9DBD-F9D1BD09C9DF}"/>
+  <xr:revisionPtr revIDLastSave="1617" documentId="8_{14C11024-DAA1-4BC8-A0C0-1702803526E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673B512C-5BF3-409C-83DA-27793659718D}"/>
   <bookViews>
-    <workbookView xWindow="-4032" yWindow="-17280" windowWidth="15552" windowHeight="16656" firstSheet="6" activeTab="7" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-4044" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Ter discussie" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -161,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="356">
   <si>
     <t>Veld</t>
   </si>
@@ -1330,6 +1331,9 @@
   </si>
   <si>
     <t>Waarom zetten we groep er wel of niet bij? Nu niet meegenomen, maar wellicht voor in de toekomst?</t>
+  </si>
+  <si>
+    <t>clici</t>
   </si>
 </sst>
 </file>
@@ -1667,96 +1671,6 @@
   </cellStyles>
   <dxfs count="23">
     <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1868,6 +1782,96 @@
         <scheme val="minor"/>
       </font>
       <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2638,9 +2642,9 @@
   <autoFilter ref="A2:F13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{DAF348AE-F547-4357-9E3C-18B833059F60}" name="Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6782DEBA-8C39-4E2C-BBC2-2CD68FCA1048}" name="Bronnen" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{DAF348AE-F547-4357-9E3C-18B833059F60}" name="Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{6782DEBA-8C39-4E2C-BBC2-2CD68FCA1048}" name="Bronnen" dataDxfId="14"/>
     <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
     <tableColumn id="6" xr3:uid="{1CF171A1-4997-44CE-A155-D2A5B879A058}" name="a.d.h.v. keuze OpenEHR als basismodel"/>
   </tableColumns>
@@ -2649,36 +2653,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N50" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N50" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A2:N50" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
     <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2697,13 +2701,13 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E8" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E8" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="B3:E8" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{560ECDF4-85E6-4E09-A58E-EF7D363E1023}" name="Data element" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7F322FC5-2406-403F-A6D2-4B8A1403332A}" name="Informatiestandaard" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{735B888A-5B6D-4761-9CE2-3D7CE959A3F7}" name="Uitleg" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{B46EF00D-8E8C-4C31-9A1B-A5AED42F9E48}" name="Uitkomst" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{560ECDF4-85E6-4E09-A58E-EF7D363E1023}" name="Data element" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{7F322FC5-2406-403F-A6D2-4B8A1403332A}" name="Informatiestandaard" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{735B888A-5B6D-4761-9CE2-3D7CE959A3F7}" name="Uitleg" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{B46EF00D-8E8C-4C31-9A1B-A5AED42F9E48}" name="Uitkomst" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3609,7 +3613,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
@@ -3969,7 +3973,9 @@
       <c r="A16" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="10"/>
+      <c r="B16" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="C16" s="10" t="s">
         <v>161</v>
       </c>
@@ -4093,7 +4099,7 @@
       <c r="D20" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="10" t="s">
         <v>183</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -4816,7 +4822,7 @@
       <c r="D46" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="10" t="s">
         <v>302</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -5204,6 +5210,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5410,15 +5425,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5431,6 +5437,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5449,14 +5463,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl.sharepoint.com/sites/Zib-transitiecommunity/Gedeelde documenten/Architectuur/Werkgroepen ZIBS 2.0 Implementatie/Bouwblokken/Condition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1617" documentId="8_{14C11024-DAA1-4BC8-A0C0-1702803526E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673B512C-5BF3-409C-83DA-27793659718D}"/>
+  <xr:revisionPtr revIDLastSave="1810" documentId="8_{14C11024-DAA1-4BC8-A0C0-1702803526E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FA77EFC-A93B-4D05-99C9-4A0BE8DE9C03}"/>
   <bookViews>
-    <workbookView xWindow="-4044" yWindow="-17388" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -53,7 +53,6 @@
     <author>tc={DC3A08E9-01DD-48D1-B7F5-357810DE5428}</author>
     <author>tc={035A58F6-6A6B-4788-883F-2110C3BA07ED}</author>
     <author>tc={00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}</author>
-    <author>Shenaida Hoogland</author>
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
@@ -65,7 +64,7 @@
     AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
       </text>
     </comment>
-    <comment ref="J19" authorId="1" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
+    <comment ref="J21" authorId="1" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -77,7 +76,7 @@
  evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="2" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <comment ref="K21" authorId="2" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -87,7 +86,7 @@
 Kortere waardelijst</t>
       </text>
     </comment>
-    <comment ref="K23" authorId="3" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+    <comment ref="K26" authorId="3" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -95,7 +94,7 @@
     Wel in metadata!</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="4" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="E29" authorId="4" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -103,7 +102,7 @@
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B28" authorId="5" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B31" authorId="5" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -111,7 +110,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C28" authorId="6" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C31" authorId="6" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -119,37 +118,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="B32" authorId="7" shapeId="0" xr:uid="{DF16D6DB-6BF2-4105-935F-CAE9E0779508}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Shenaida Hoogland:
-ter discussie</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C32" authorId="7" shapeId="0" xr:uid="{5C2BCC1D-F15F-46C8-B26A-850B59225D39}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Shenaida Hoogland:
-ter discussie</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C36" authorId="8" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C39" authorId="7" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="385">
   <si>
     <t>Veld</t>
   </si>
@@ -360,9 +329,6 @@
     <t>Ja</t>
   </si>
   <si>
-    <t>Condition model - EHDS Logical Information Models v1.0.0</t>
-  </si>
-  <si>
     <t>FHIR R4 resource Condition</t>
   </si>
   <si>
@@ -507,9 +473,6 @@
     <t>Subject</t>
   </si>
   <si>
-    <t>De patiënt waarover de conditie gaat</t>
-  </si>
-  <si>
     <t>Verwijzing naar Patient</t>
   </si>
   <si>
@@ -525,9 +488,6 @@
     <t>Subject of care</t>
   </si>
   <si>
-    <t xml:space="preserve">De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. </t>
-  </si>
-  <si>
     <t>Vewijzing naar Subject of Care</t>
   </si>
   <si>
@@ -537,18 +497,9 @@
     <t>CON-1.3</t>
   </si>
   <si>
-    <t>Wie heeft de conditie?</t>
-  </si>
-  <si>
-    <t>Verwijziging naar Patient of Group</t>
-  </si>
-  <si>
     <t>CON-2</t>
   </si>
   <si>
-    <t>Identificatie van object Conditie</t>
-  </si>
-  <si>
     <t>Ja (identifier)</t>
   </si>
   <si>
@@ -585,18 +536,9 @@
     <t>CON-3</t>
   </si>
   <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Degene die de informatie over de conditie heeft geschreven</t>
-  </si>
-  <si>
     <t>0..* Choice of types</t>
   </si>
   <si>
-    <t>Ja (recorder, 0..1)</t>
-  </si>
-  <si>
     <t>Ja (RM:other_participations)</t>
   </si>
   <si>
@@ -609,9 +551,6 @@
     <t>authorEHDSHealthProfessional</t>
   </si>
   <si>
-    <t>De zorgverlener die de informatie over de conditie heeft geschreven</t>
-  </si>
-  <si>
     <t>Verwijziging naar EHDSHealthProfessional</t>
   </si>
   <si>
@@ -630,9 +569,6 @@
     <t>authorEHDSOrganisation</t>
   </si>
   <si>
-    <t>De organisatie waaruit de informatie over de conditie afkomstig is</t>
-  </si>
-  <si>
     <t>Verwijziging naar EHDSOrganization</t>
   </si>
   <si>
@@ -648,27 +584,18 @@
     <t>authorEHDSDevice</t>
   </si>
   <si>
-    <t>Het invoerapparaat van de informatie over de conditie</t>
-  </si>
-  <si>
     <t>Verwijziging naar EHDSDevice</t>
   </si>
   <si>
     <t>CON-4</t>
   </si>
   <si>
-    <t>Datum en evt. tijd van rergistreren</t>
-  </si>
-  <si>
     <t>CON-4.1</t>
   </si>
   <si>
     <t>header.date</t>
   </si>
   <si>
-    <t>De datum en evt. tijd waarop het object is geschreven</t>
-  </si>
-  <si>
     <t>DatumTijd</t>
   </si>
   <si>
@@ -684,32 +611,6 @@
     <t>CON-4.2</t>
   </si>
   <si>
-    <t>registratiedatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Startdatum </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-&gt; waarom is deze datum nodig als een verplichting? Wat wil je met de informatie. moet het een timestamp tot microseconde is geregistreerd. Als we het niet kunnen vinden dan schrijven we dat ook in de variabiliteit dat mogelijk een vagere datumTijd ook mag</t>
-    </r>
-  </si>
-  <si>
     <t>Time Stamp</t>
   </si>
   <si>
@@ -723,12 +624,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>De status van de conditie</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): HL7 Condition Clinical Status Codes (active, recurrence, relapse, inactive, remission, resolved, unknown)</t>
   </si>
   <si>
     <t>Ja (clinicalStatus)</t>
@@ -749,9 +644,6 @@
 Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
   </si>
   <si>
-    <t>Waardelijst (actief, inactief)</t>
-  </si>
-  <si>
     <t>Spoedsamenvatting 2.2.0; Zib 2017; zib 2020</t>
   </si>
   <si>
@@ -761,25 +653,16 @@
     <t>CON-6</t>
   </si>
   <si>
-    <t>source</t>
-  </si>
-  <si>
     <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf</t>
   </si>
   <si>
     <t xml:space="preserve">Gecodeerde concept </t>
   </si>
   <si>
-    <t>Ja (asserter)</t>
-  </si>
-  <si>
     <t>Ja (Reference model: Information Provider) 0..1 Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software.</t>
   </si>
   <si>
     <t>CON-7</t>
-  </si>
-  <si>
-    <t>language</t>
   </si>
   <si>
     <t>De taal waarin het object is geschreven</t>
@@ -918,12 +801,6 @@
   </si>
   <si>
     <t>CON-9.3</t>
-  </si>
-  <si>
-    <t>zorgpepisode.startdatum</t>
-  </si>
-  <si>
-    <t>Bij een episode kan zowel de startdatum van de episode zelf (het begin van de contacten tussen arts en patiënt over een gezondheidskwestie) worden vastgelegd, als de begindatum van de in de episodetitel beschreven aandoening.</t>
   </si>
   <si>
     <t>CON-10</t>
@@ -1333,14 +1210,304 @@
     <t>Waarom zetten we groep er wel of niet bij? Nu niet meegenomen, maar wellicht voor in de toekomst?</t>
   </si>
   <si>
-    <t>clici</t>
+    <t>2.16.840.1.113883.2.4.3.11.60.153.4.30/2026-07-29T00:00:00</t>
+  </si>
+  <si>
+    <t>Identificatie van object gezondheidstoestand</t>
+  </si>
+  <si>
+    <t>De patiënt waarover de gezondheidstoestand gaat</t>
+  </si>
+  <si>
+    <t>Verwijziging naar Patient of Groep</t>
+  </si>
+  <si>
+    <t>De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. In bepaalde omstandigheden kan het echter ook om anderen gaan, bijvoorbeeld een orgaandonor, een foetus of een familielid.</t>
+  </si>
+  <si>
+    <t>Geeft aan aan welke patiënt of groep het dossier in kader van gezondheidstoestand is gekoppeld.</t>
+  </si>
+  <si>
+    <t>CON-1.4</t>
+  </si>
+  <si>
+    <t>Nee, Kenmerken die relevant zijn voor een eenduidige definitie van het concept vormen de dataelementen van de zib. Een zib moet alle mogelijke eigenschappen van dat concept vatten voor zover relevant in gebruik van informatiesystemen binnen het zorg- en gezondheidsdomein
+Kenmerken die wel relevant zijn voor een compleet begrip, maar ook los van het concept herbruikbaar zijn worden als aparte zib middels een relaties vormgegeven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nee </t>
+  </si>
+  <si>
+    <t>CON-3.4</t>
+  </si>
+  <si>
+    <t>contactpersoon als auteur</t>
+  </si>
+  <si>
+    <t>auteur</t>
+  </si>
+  <si>
+    <t>nee</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EHDSCondition.header.author</t>
+  </si>
+  <si>
+    <t>LIMS omschrijving is "	
+The author of the condition information."  Het is gemapt met FHIR: Condition.recorder: de omschrijving is "Individual who recorded the record and takes responsibility for its content." -&gt; de registratie-persoon is niet altijd ook de verantwoordelijke.  Is dit een foute mapping?</t>
+  </si>
+  <si>
+    <t>Verwijzing naar patient, zorgverlener, contactpersoon</t>
+  </si>
+  <si>
+    <t>CON-6.1</t>
+  </si>
+  <si>
+    <t>Degene die de informatie heeft verschaft en instaat voor de juistheid ervan. Dit is niet altijd zorgverlener die de gegevens invoert in het informatiesysteem, maar het kan ook de patiënt zijn of een andere betrokkene zoals bv een ouder, mantelzorger of voogd.</t>
+  </si>
+  <si>
+    <t>Informatiebron</t>
+  </si>
+  <si>
+    <t>Het apparaat waar de informatie over de conditie vandaan komt</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ja (asserter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>ja, informatiebron als basiselement</t>
+  </si>
+  <si>
+    <t>nee, niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.</t>
+  </si>
+  <si>
+    <t>JA, auteur als basiselement</t>
+  </si>
+  <si>
+    <t>Auteur: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot bron van de informatie en de vastlegger in het dossier.</t>
+  </si>
+  <si>
+    <t>Zib 2017 https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf</t>
+  </si>
+  <si>
+    <t>Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf)</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0, Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+Spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0
+spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ja (recorder </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 0..1)</t>
+    </r>
+  </si>
+  <si>
+    <t>ZIB 2017  (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+Spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>NL-behoefte vanuit 2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
+NL-behoefte komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
+  </si>
+  <si>
+    <t>Om het object uniek te identificeren in systemen</t>
+  </si>
+  <si>
+    <t>De auteur van de informatie over de gezondheidstoestand.
+NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
+NL-behoefte komt te vervallen in zib2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De organisatie waaruit de informatie over de conditie afkomstig is.
+NL-behoefte: waarom/meerwaarde vanuit de spoedsamenvatting: om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; als in er kunnen verschillende zorgverleners werken bij dezelfde organisatie.-&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit  HL7standaard V3 CDA (custiodian en author) 
+Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder (bron: https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf ). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+De zorgverlener die de informatie over de conditie invoert/registreert
+NL-behoefte: Waarom/meerwaarde vanuit de spoedsamenvatting; om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; Er kunnen verschillende zorgverleners werken bij dezelfde organisatie -&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit HL7standaard V3 CDA (custiodian en author) 
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NL-behoefte zib2017: Degene die de informatie heeft vastgelegd. Afhankelijk van het informatiesysteem waarin de gegevens vastgelegd zijn kan dit zijn de patiënt, een </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">contactpersoon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of de zorgverlener.  Het is  een basiselementen. Deze zijn in de informatiemodellen van de afzonderlijke bouwstenen in de meeste gevallen niet opgenomen, maar worden wel verondersteld aanwezig te zijn. Het betreft concepten die meer technisch van aard zijn, vaak geen of weinig klinische relevantie hebben, maar voor de eenduidigheid en herleidbaarheid van de gegevens noodzakelijk zijn.
+NL-behoefte komt te vervallen in zib2020</t>
+    </r>
+  </si>
+  <si>
+    <t>Datum en evt. tijd van registreren</t>
+  </si>
+  <si>
+    <t>Datum en eventueel tijdstip van opstellen/uitgeven</t>
+  </si>
+  <si>
+    <t>Bij een episode kan zowel de startdatum van de episode zelf (het begin van de contacten tussen arts en patiënt over een gezondheidskwestie) worden vastgelegd, als de begindatum van de in de episodetitel beschreven aandoening.
+Bij template kezo-Problemobservation  is De effectiveTime, ook biologisch relevante tijd genoemd, is het tijdstip waarop de waarneming geldt voor de patient. Voor een zorgverlener die een patiënt in de kliniek vandaag ziet en waar een voorgeschiedenis van een hartaanval wordt geconstatterd die vijf jaar geleden heeft plaatsgevonden, is de effectiveTime dus vijf jaar geleden.
+de reden voor IVL_TS is onbekend</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0 (https://decor.nictiz.nl/pub/acutezorg/acutezorg-html-20190117T230242/tmp-2.16.840.1.113883.2.4.3.11.60.66.10.213-2015-07-03T000000.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zorgepisode.startdatum </t>
+  </si>
+  <si>
+    <t>probleem.startdatum</t>
+  </si>
+  <si>
+    <t>IVL_TS</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0 (bron: KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212)</t>
+  </si>
+  <si>
+    <t>NL-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; cardinaliteit 1</t>
+  </si>
+  <si>
+    <t>https://referentiemodel.nhg.org/
+https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>Bron</t>
+  </si>
+  <si>
+    <t>Taal</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Condition model - EHDS Logical Information Models v1.0.0
+https://health.ec.europa.eu/publications/ehn-guideline-patient-summary_en</t>
+  </si>
+  <si>
+    <t>De status van de conditie. Requirement: eHN Guideline HDR (v1.1): A.2.6.1.7; PS (v3.4) A.2.2.2.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">Waardelijst (preferred): HL7 Condition Clinical Status Codes (active, recurrence, relapse, inactive, remission, resolved, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>unknown?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>PAT-301</t>
+    </r>
+  </si>
+  <si>
+    <t>datumTijd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1461,6 +1628,29 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1563,7 +1753,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1634,9 +1824,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1664,6 +1851,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2580,55 +2786,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2880360</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Afbeelding 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{003B378A-E260-9EB9-1F30-F75DD4C8CACD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="5943600"/>
-          <a:ext cx="6667500" cy="3781425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Chevy Susanto" id="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" userId="S::chevy.susanto@nictiz.nl::4e93d0cc-e599-42c6-82b7-6ffb715c7e27" providerId="AD"/>
@@ -2667,8 +2824,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N50" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A2:N50" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A2:N53" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="4"/>
@@ -2701,8 +2858,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E8" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="B3:E8" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E9" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="B3:E9" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{560ECDF4-85E6-4E09-A58E-EF7D363E1023}" name="Data element" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{7F322FC5-2406-403F-A6D2-4B8A1403332A}" name="Informatiestandaard" dataDxfId="19"/>
@@ -3033,31 +3190,31 @@
   <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
     <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
   </threadedComment>
-  <threadedComment ref="J19" dT="2026-07-16T05:50:21.33" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
+  <threadedComment ref="J21" dT="2026-07-16T05:50:21.33" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
     <text> active
  inactive
  resolved
  in remission
  evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</text>
   </threadedComment>
-  <threadedComment ref="K19" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+  <threadedComment ref="K21" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
     <text>1. Actief
 2. Inactief
 Kortere waardelijst</text>
   </threadedComment>
-  <threadedComment ref="K23" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+  <threadedComment ref="K26" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
     <text>Wel in metadata!</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+  <threadedComment ref="E29" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
   </threadedComment>
-  <threadedComment ref="B28" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+  <threadedComment ref="B31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C28" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+  <threadedComment ref="C31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C36" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C39" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
   </threadedComment>
 </ThreadedComments>
@@ -3214,7 +3371,7 @@
       <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="36" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3290,6 +3447,9 @@
       <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -3297,7 +3457,7 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -3347,7 +3507,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
@@ -3360,8 +3520,8 @@
       <c r="D2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>60</v>
+      <c r="E2" s="4" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -3369,10 +3529,10 @@
         <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>59</v>
@@ -3386,96 +3546,100 @@
         <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3534,7 +3698,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{6EB8E4BD-B940-48E6-A6CE-4F11C1A8510E}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{F95A6B3D-7F5D-4E74-8C6D-B30290D6ED58}"/>
+    <hyperlink ref="E2" r:id="rId2" display="Condition model - EHDS Logical Information Models v1.0.0" xr:uid="{F95A6B3D-7F5D-4E74-8C6D-B30290D6ED58}"/>
     <hyperlink ref="E7" r:id="rId3" xr:uid="{612DD86C-3891-43E3-B27A-AA6071C8917D}"/>
     <hyperlink ref="E6" r:id="rId4" xr:uid="{104C1F39-D7B8-4AE4-9031-EE6CE3C7F3A7}"/>
     <hyperlink ref="E5" r:id="rId5" xr:uid="{B27B79EC-18DD-4070-9630-609E711CCC3B}"/>
@@ -3550,12 +3714,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="87.44140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="26.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" customWidth="1"/>
@@ -3571,78 +3735,78 @@
     <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
         <v>81</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>82</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>96</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>102</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>103</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21"/>
@@ -3651,38 +3815,42 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
       <c r="I4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K4" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+        <v>337</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>337</v>
+      </c>
       <c r="N4" s="21"/>
       <c r="O4" s="9"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="D5" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3691,26 +3859,26 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>334</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3721,24 +3889,24 @@
     </row>
     <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>119</v>
+        <v>335</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>120</v>
+        <v>333</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3747,287 +3915,298 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="F8" s="3"/>
+    <row r="8" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="H8" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>126</v>
-      </c>
+    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="8"/>
       <c r="D9" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>128</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>363</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>146</v>
+        <v>359</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>130</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="3"/>
+        <v>354</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L13" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>156</v>
+        <v>364</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>112</v>
+        <v>358</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>158</v>
+      <c r="A15" s="21" t="s">
+        <v>142</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>162</v>
+    <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>366</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>112</v>
+        <v>356</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>166</v>
+        <v>342</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>111</v>
-      </c>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -4035,80 +4214,82 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="3"/>
+    <row r="18" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="41" t="s">
+        <v>148</v>
+      </c>
       <c r="D18" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>175</v>
+        <v>153</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>176</v>
+        <v>375</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>177</v>
+        <v>373</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>175</v>
-      </c>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>111</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>184</v>
-      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -4116,406 +4297,407 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F21" s="3"/>
+    <row r="21" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>383</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" s="10"/>
+        <v>165</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="D22" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>189</v>
+        <v>163</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>384</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>106</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>193</v>
+        <v>378</v>
       </c>
       <c r="C23" s="10"/>
-      <c r="D23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="44"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="F24" s="3"/>
+    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="39"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>201</v>
+        <v>350</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>169</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="L24" s="3"/>
+        <v>352</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>351</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3" t="s">
-        <v>204</v>
+    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="44" t="s">
+        <v>348</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>111</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>112</v>
+        <v>355</v>
       </c>
       <c r="I25" s="3"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
-        <v>208</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="10"/>
       <c r="D26" s="3" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>111</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C29" s="10"/>
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="D29" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>226</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="I31" s="3"/>
-      <c r="J31" s="34"/>
+      <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
-        <v>235</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="10"/>
       <c r="D32" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C33" s="10"/>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="D33" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
+        <v>206</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>246</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
-        <v>247</v>
+    <row r="35" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>248</v>
+        <v>372</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>249</v>
+        <v>369</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>171</v>
+        <v>373</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -4524,153 +4706,138 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>253</v>
+        <v>212</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="C37" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="K37" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="C38" s="10"/>
+        <v>222</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="D38" s="3" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I38" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="J38" s="36" t="s">
-        <v>264</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>269</v>
-      </c>
+    <row r="39" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>271</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="3" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>277</v>
+        <v>232</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>233</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -4679,80 +4846,96 @@
     </row>
     <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3" t="s">
-        <v>279</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
-        <v>280</v>
+        <v>236</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>239</v>
+      </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3" t="s">
-        <v>282</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
-        <v>283</v>
+        <v>242</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G42" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="H42" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="J43" s="26" t="s">
-        <v>289</v>
+        <v>251</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4760,18 +4943,25 @@
       <c r="N43" s="3"/>
     </row>
     <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="F44" s="3"/>
+      <c r="A44" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
+      <c r="H44" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="I44" s="3"/>
-      <c r="J44" s="26"/>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4779,93 +4969,74 @@
     </row>
     <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="22" t="s">
-        <v>293</v>
+        <v>256</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J45" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="K45" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
+        <v>210</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="22" t="s">
-        <v>300</v>
-      </c>
+    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C46" s="10"/>
       <c r="D46" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>302</v>
+        <v>261</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="s">
-        <v>303</v>
+      <c r="A47" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="C47" s="10"/>
-      <c r="D47" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="J47" s="22" t="s">
-        <v>308</v>
-      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="26"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -4873,102 +5044,196 @@
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C48" s="10"/>
+        <v>267</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="22" t="s">
+        <v>268</v>
+      </c>
       <c r="D48" s="3" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>313</v>
+        <v>150</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
+        <v>271</v>
+      </c>
+      <c r="J48" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="30"/>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="22" t="s">
+        <v>275</v>
+      </c>
       <c r="D49" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>262</v>
+        <v>276</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+        <v>210</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B50" t="s">
-        <v>321</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>322</v>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H50" t="s">
-        <v>324</v>
-      </c>
-      <c r="I50" t="s">
-        <v>325</v>
-      </c>
-      <c r="J50" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-    </row>
-    <row r="55" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="32"/>
-      <c r="C55" s="33"/>
-    </row>
-    <row r="56" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
+        <v>281</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="29"/>
+      <c r="D52" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B53" t="s">
+        <v>296</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H53" t="s">
+        <v>299</v>
+      </c>
+      <c r="I53" t="s">
+        <v>300</v>
+      </c>
+      <c r="J53" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+    </row>
+    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="31"/>
+      <c r="C58" s="32"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -4997,48 +5262,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5055,7 +5320,7 @@
     <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -5075,7 +5340,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="B1" t="s">
         <v>53</v>
@@ -5083,15 +5348,15 @@
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -5104,7 +5369,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
-  <dimension ref="A2:J8"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" style="3" customWidth="1"/>
@@ -5115,7 +5380,7 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -5123,52 +5388,52 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="16" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21"/>
       <c r="B6" s="3" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5178,33 +5443,42 @@
     </row>
     <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="39" t="s">
-        <v>352</v>
+      <c r="D8" s="38" t="s">
+        <v>327</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>354</v>
-      </c>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="B9" s="42"/>
+      <c r="C9" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>344</v>
+      </c>
+      <c r="E9" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl.sharepoint.com/sites/Zib-transitiecommunity/Gedeelde documenten/Architectuur/Werkgroepen ZIBS 2.0 Implementatie/Bouwblokken/Condition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichalCiszewski\Documents\Github\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1810" documentId="8_{14C11024-DAA1-4BC8-A0C0-1702803526E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FA77EFC-A93B-4D05-99C9-4A0BE8DE9C03}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1320D0F2-528E-4561-A815-608E3850C934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="Ter discussie" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,17 +57,17 @@
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
       </text>
     </comment>
     <comment ref="J21" authorId="1" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
      active
  inactive
  resolved
@@ -78,9 +77,9 @@
     </comment>
     <comment ref="K21" authorId="2" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     1. Actief
 2. Inactief
 Kortere waardelijst</t>
@@ -88,41 +87,41 @@
     </comment>
     <comment ref="K26" authorId="3" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Wel in metadata!</t>
       </text>
     </comment>
     <comment ref="E29" authorId="4" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
     <comment ref="B31" authorId="5" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
     <comment ref="C31" authorId="6" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
     <comment ref="C39" authorId="7" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
@@ -1753,7 +1752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1851,21 +1850,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1873,122 +1857,9 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment wrapText="1"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -2078,6 +1949,119 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2799,9 +2783,9 @@
   <autoFilter ref="A2:F13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{DAF348AE-F547-4357-9E3C-18B833059F60}" name="Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{6782DEBA-8C39-4E2C-BBC2-2CD68FCA1048}" name="Bronnen" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{DAF348AE-F547-4357-9E3C-18B833059F60}" name="Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6782DEBA-8C39-4E2C-BBC2-2CD68FCA1048}" name="Bronnen" dataDxfId="13"/>
     <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
     <tableColumn id="6" xr3:uid="{1CF171A1-4997-44CE-A155-D2A5B879A058}" name="a.d.h.v. keuze OpenEHR als basismodel"/>
   </tableColumns>
@@ -2810,36 +2794,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="A2:N53" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="20"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="18"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
     <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="16"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2858,13 +2842,13 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E9" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E9" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B3:E9" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{560ECDF4-85E6-4E09-A58E-EF7D363E1023}" name="Data element" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{7F322FC5-2406-403F-A6D2-4B8A1403332A}" name="Informatiestandaard" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{735B888A-5B6D-4761-9CE2-3D7CE959A3F7}" name="Uitleg" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{B46EF00D-8E8C-4C31-9A1B-A5AED42F9E48}" name="Uitkomst" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{560ECDF4-85E6-4E09-A58E-EF7D363E1023}" name="Data element" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{7F322FC5-2406-403F-A6D2-4B8A1403332A}" name="Informatiestandaard" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{735B888A-5B6D-4761-9CE2-3D7CE959A3F7}" name="Uitleg" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{B46EF00D-8E8C-4C31-9A1B-A5AED42F9E48}" name="Uitkomst" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3836,7 +3820,7 @@
       <c r="A5" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -3916,10 +3900,10 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B8" s="40"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
         <v>308</v>
       </c>
@@ -3968,7 +3952,7 @@
       <c r="A10" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -4163,10 +4147,10 @@
       <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="3" t="s">
         <v>340</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -4219,7 +4203,7 @@
         <v>147</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4301,13 +4285,13 @@
       <c r="A21" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="3" t="s">
         <v>158</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="40" t="s">
         <v>383</v>
       </c>
       <c r="F21" s="3" t="s">
@@ -4371,13 +4355,13 @@
       <c r="I23" s="3"/>
       <c r="J23" s="25"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="44"/>
+      <c r="L23" s="39"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
-      <c r="B24" s="41"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="25" t="s">
         <v>380</v>
       </c>
@@ -4403,18 +4387,18 @@
       <c r="K24" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="L24" s="44" t="s">
+      <c r="L24" s="39" t="s">
         <v>351</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="44" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="39" t="s">
         <v>348</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -5466,14 +5450,14 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="43"/>
+      <c r="E9" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5484,15 +5468,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5699,6 +5674,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5711,14 +5695,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5737,6 +5713,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichalCiszewski\Documents\Github\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1320D0F2-528E-4561-A815-608E3850C934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455916BA-1B1A-461D-977E-85F4A305936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
-    <sheet name="Concept" sheetId="2" r:id="rId2"/>
+    <sheet name="Concept" sheetId="9" r:id="rId2"/>
     <sheet name="Bronnen" sheetId="6" r:id="rId3"/>
     <sheet name="Informatiebehoefte" sheetId="1" r:id="rId4"/>
     <sheet name="Ongedekte informatiebehoefte" sheetId="3" r:id="rId5"/>
@@ -22,6 +22,12 @@
     <sheet name="Basismodel" sheetId="7" r:id="rId7"/>
     <sheet name="Ter discussie" sheetId="8" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="Informatiebron">[1]!Tabel3[Naam bron]</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -130,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="353">
   <si>
     <t>Veld</t>
   </si>
@@ -138,151 +144,52 @@
     <t>Beschrijving</t>
   </si>
   <si>
-    <t>Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)</t>
-  </si>
-  <si>
-    <t>Bronnen</t>
-  </si>
-  <si>
-    <t>a.d.h.v. keuze FHIR als basismodel</t>
-  </si>
-  <si>
-    <t>a.d.h.v. keuze OpenEHR als basismodel</t>
-  </si>
-  <si>
     <t>Conceptbeschrijving</t>
   </si>
   <si>
-    <t>[De definitie of beschrijving van het concept.]</t>
-  </si>
-  <si>
     <t>Een conditie beschrijft een klinisch relevante gezondheidstoestand, diagnose, probleem, aandoening of andere gezondheidsituatie die betrekking heeft op de gezondheid en/of het welzijn van de patiënt. Deze toestand kan benoemd zijn door de patiënt, gerelateerd persoon of door de zorgverlener. De gezondheidstoestand kan aanleiding geven tot behandeling, monitoring of vervolgbeleid.</t>
   </si>
   <si>
-    <t>Samengesteld uit EHDS LIM EHDSCondition v1.0.0; FHIR R4 Condition; openEHR problem/Diagnosis v1.5.0; zib Probleem 2020</t>
-  </si>
-  <si>
-    <t>Een klinische aandoening, probleem, diagnose of andere gebeurtenis, situatie, kwestie of klinisch concept dat aanleiding geeft tot zorg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details over een specifieke gezondheidstoestand, letsel, handicap of ander probleem dat van invloed is op het fysieke, mentale en/of sociale welzijn van een individu.
-Opmerking: In de praktijk is het niet eenvoudig om een ​​duidelijke scheiding te maken tussen de omvang van een probleem en een diagnose. Voor klinische documentatie met dit archetype worden probleem en diagnose beschouwd als een continuüm, waarbij toenemende mate van detail en ondersteunend bewijs doorgaans meer gewicht toekennen aan het label 'diagnose'.
-</t>
-  </si>
-  <si>
-    <t>EDHS LIM: Model for a clinical condition, problem, diagnosis, or other event, situation, or issue that has risen to a level of concern.
-OpenEHR: 
-ChatGPT samenvatting van FHIR R4 resource: Model voor klinisch relevante gezondheidstoestand van een patiënt die door een zorgverlener zijn beoordeeld of vastgesteld. Dit kan een diagnose, gezondheidsprobleem, zorgvraag of andere gezondheidssituatie zijn die aanleiding geeft tot behandeling, monitoring of vervolgbeleid.
-Zib Probleem 2020: Een probleem beschrijft een toestand met betrekking tot de gezondheid en/of het welzijn van een individu. Deze toestand kan zijn benoemd door de betroffene (de patiënt) zelf (een klacht), of door zijn of haar zorgverlener (onder andere een diagnose). De toestand kan aanleiding zijn voor diagnostisch of therapeutisch beleid.
-Een probleem omvat allerlei soorten medische of verpleegkundige gegevens, die een gezondheidsprobleem representeren. Een probleem kan verschillende typen gezondheidsproblemen representeren: symptoom, klacht, diagnose, functionele beperking, complicatie. 
-OpenEHR: Details over een specifieke gezondheidstoestand, letsel, handicap of ander probleem dat van invloed is op het fysieke, mentale en/of sociale welzijn van een persoon.</t>
-  </si>
-  <si>
     <t>Doel</t>
   </si>
   <si>
-    <t>[De doelen en redenen om het concept vast te leggen en/of uit te wisselen.]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Een overzicht van gezondheidstoestanden/diagnoses/aandoeningen van de patient. </t>
   </si>
   <si>
-    <t>Gedestileerd uit de conceptbeschrijving</t>
-  </si>
-  <si>
-    <t>Het doel van het concept is het eenduidig vastleggen en uitwisselen van een klinisch relevante diagnose, aandoening, gezondheidstoestand of ander zorgpunt van een patiënt. Dit ondersteunt nader onderzoek, behandeling, monitoring en overdracht van zorg, ook wanneer het gaat om een niet-negatieve gezondheidstoestand, zoals zwangerschap, of om een toestand die het gevolg is van een eerdere ingreep.</t>
-  </si>
-  <si>
-    <t>Voor het vastleggen van details over een enkel, geïdentificeerd gezondheidsprobleem of diagnose.
-De beoogde reikwijdte van een gezondheidsprobleem wordt in de context van klinische documentatie bewust ruim gehouden, zodat alle reële of vermeende zorgen die het welzijn van een persoon in welke mate dan ook negatief kunnen beïnvloeden, kunnen worden vastgelegd. Een gezondheidsprobleem kan worden geïdentificeerd door de persoon zelf, een mantelzorger of een zorgverlener. Een diagnose wordt echter daarnaast gedefinieerd op basis van objectieve klinische criteria en wordt doorgaans alleen vastgesteld door een zorgverlener.</t>
-  </si>
-  <si>
     <t>Gebruiksscenario(’s)</t>
-  </si>
-  <si>
-    <t>[Geeft aan in welke context(en) het concept wordt gebruikt. Geef voorbeelden van gebruik in informatiestandaarden.]</t>
   </si>
   <si>
     <t>Een overzicht van gezondheidstoestanden/diagnoses/aandoeningen van de patient. Het wordt gebruikt in de informatiestandaarden BgZ-MSZ, Eerstelijnszorg, .. 
 Conditie kan worden gebruikt om het gezondheidsprobleem in een zorgepisode te duiden.</t>
   </si>
   <si>
-    <t>Afkomstig uit informatiestandaard BgZ-MSZ, informatiestandaard Acute Zorg</t>
-  </si>
-  <si>
-    <t>Het kan worden gebruikt om informatie vast te leggen over een ziekte of aandoening die is vastgesteld op basis van klinische redenering over pathologische en pathofysiologische bevindingen (diagnose); over gezondheidsproblemen of -situaties die een zorgverlener als schadelijk of potentieel schadelijk beschouwt en die nader onderzoek en behandeling vereisen (probleem); of over andere gezondheidsproblemen of -situaties die mogelijk voortdurende monitoring en/of behandeling behoeven (gezondheidsprobleem/-zorgpunt).
-De 'Condition'-resource kan worden gebruikt om een ​​bepaalde gezondheidstoestand van een patiënt vast te leggen die doorgaans niet als een negatieve uitkomst wordt beschouwd, zoals zwangerschap. De 'Condition'-resource kan ook worden gebruikt om een ​​aandoening of toestand vast te leggen die volgt op een ingreep, zoals de status van 'onderbeenamputatiepatiënt' na een amputatieprocedure.
-Spoedsamenvatting 2.2.0, bij het opstellen van de episodes en problemen 
-BgZ-MSZ: bij klachten en diagnoses
-eOverdracht: problemen
-Eerstelijnszorg: problemen</t>
-  </si>
-  <si>
-    <t>Dit archetype kan in veel contexten worden gebruikt. Bijvoorbeeld om een ​​probleem of een klinische diagnose vast te leggen tijdens een consult; om een ​​permanente probleemlijst aan te vullen; of om een ​​samenvattende verklaring op te nemen in een ontslagbrief.</t>
-  </si>
-  <si>
     <t>Representatie</t>
   </si>
   <si>
-    <t>[Beschrijf hier wat er voor de dossiervorming belangrijk is rondom de levenscyclus en instantiaties van het concept.]</t>
-  </si>
-  <si>
     <t>Een gezondheidsstoestand heeft een start en kan een einddatum hebben, maar hoeft niet. Het kan gevlagt zijn om in de probleemlijst van de patient aanwezig te blijven, ook al is de gezondheidsstoestand opgeheven.</t>
   </si>
   <si>
-    <t>Gedestileerd uit de data-elementen van de EHDS LIM EHDSCondition v1.0.0</t>
-  </si>
-  <si>
-    <t>Een instantiatie beschrijft één klinisch relevante conditie bij een patiënt. Veranderingen in status of zekerheid worden in dezelfde registratie bijgewerkt; voor een andere conditie of afzonderlijke episode wordt een nieuwe instantiatie gemaakt. Beëindigde of weerlegde condities blijven als historie beschikbaar.</t>
-  </si>
-  <si>
-    <t>kijken hoe openEHR erover denkt met evoluerende diagnose van de patient.</t>
-  </si>
-  <si>
     <t>Alias(sen)</t>
   </si>
   <si>
-    <t>[Alle bekende synoniemen voor het concept.]</t>
-  </si>
-  <si>
     <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening)</t>
   </si>
   <si>
     <t>Juist gebruik</t>
   </si>
   <si>
-    <t>[Beschrijf hier waarvoor het concept wél bedoeld is].</t>
-  </si>
-  <si>
     <t>Voor het vastleggen van diagnoses, probleem, en andere situaties van de patiënt die geen negatieve uitkomst hebben. zoals een zwangerschap.</t>
   </si>
   <si>
-    <t>Het concept is bedoeld voor het vastleggen van een klinisch relevante aandoening, diagnose, probleem, gezondheidstoestand, risico of zorgpunt dat beoordeling, behandeling of monitoring vereist.</t>
-  </si>
-  <si>
-    <t>Te gebruiken voor het vastleggen van details over een enkel, geïdentificeerd gezondheidsprobleem of diagnose.
-Duidelijke definities die onderscheid maken tussen een 'probleem' en een 'diagnose' zijn in de praktijk vrijwel onmogelijk - we kunnen niet betrouwbaar vaststellen wanneer een probleem als een diagnose moet worden beschouwd. 
-Voor klinische documentatie met dit archetype worden probleem en diagnose beschouwd als een continuüm, waarbij toenemende mate van detail en ondersteunend bewijsmateriaal doorgaans meer gewicht in de schaal legt voor de benaming 'diagnose'. In dit archetype is het niet nodig om de aandoening te classificeren als een 'probleem' of 'diagnose'.</t>
-  </si>
-  <si>
     <t>Onjuist gebruik</t>
   </si>
   <si>
-    <t>[Beschrijf hier waar het concept niet voor bedoeld is, en geef waar mogelijk aan welk concept er wel geschikt voor is.]</t>
-  </si>
-  <si>
     <t>Het wordt niet gebruikt om de functionele status, bijvoorbeeld vermogen tot ADL, vast te leggen. Het wordt niet gebruikt voor symptomen die je observeert of uitvraagt, met andere woorden wanneer een symptoom bijdraagt aan de aandoening, dient het niet opgenomen te worden als condition.</t>
   </si>
   <si>
-    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
-  </si>
-  <si>
     <t>Referenties</t>
   </si>
   <si>
-    <t>[Relevante bronstandaarden of informatiebronnen die het ontwerp en de scope van het concept hebben beïnvloed.]</t>
-  </si>
-  <si>
     <t>EHDS LIM EHDSCondition v1.0.0; FHIR R4 resource Condition; openEHR Problem/Diagnosis 1.5.0</t>
   </si>
   <si>
@@ -290,15 +197,6 @@
   </si>
   <si>
     <t>ART-DECOR-id</t>
-  </si>
-  <si>
-    <t>[Het id op ART-DECOR van het afsprakenmodel, bv 2.16.840.1.113883.2.4.3.11.60.153.4.12/2026-06-04T00:00:00]</t>
-  </si>
-  <si>
-    <t>Keuze Basismodel</t>
-  </si>
-  <si>
-    <t>Concept-sheet is opgemaakt met spelregel: https://nictiz.atlassian.net/browse/DAGIM-72</t>
   </si>
   <si>
     <t>Type bron</t>
@@ -1164,40 +1062,6 @@
   </si>
   <si>
     <t>niet in FHIR wel in openEHR. komt hier een extension voor? Device wordt nu uitgewerkt in team carefuel</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Na analyse blijkt FHIR beste keus, want:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  [hier nog even de volwassenheid van FHIR-basismodel en openEHR neerzetten]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- category geen mapping heeft op openEHR en wel een mapping op FHIR
-- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR, wel in FHIR
-- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
-- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
--specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
-    </r>
   </si>
   <si>
     <t>Indicates the patient or group who the condition record is associated with.</t>
@@ -1506,7 +1370,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1650,8 +1514,34 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1672,12 +1562,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1689,7 +1573,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1723,36 +1607,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1765,9 +1625,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1795,9 +1652,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1836,16 +1690,15 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1854,12 +1707,33 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -1951,52 +1825,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2062,6 +1890,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2194,7 +2043,7 @@
       <xdr:rowOff>223837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2181225</xdr:rowOff>
@@ -2204,7 +2053,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7E9BA32-9F57-9DBE-09F8-19BB04854D12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECAA1215-2A99-4248-92C1-D8603DD25A54}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2213,7 +2062,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="161925" y="223837"/>
-          <a:ext cx="6705600" cy="1957388"/>
+          <a:ext cx="6802755" cy="1957388"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2770,6 +2619,40 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Uitleg"/>
+      <sheetName val="Concept"/>
+      <sheetName val="Bronnen informatiebehoefte"/>
+      <sheetName val="Niet geconsolideerde info"/>
+      <sheetName val="Informatiebehoefte"/>
+      <sheetName val="Ongedekte informatiebehoefte"/>
+      <sheetName val="Overwegingen voor de toekomst"/>
+      <sheetName val="zib-centrum JIRA"/>
+      <sheetName val="Basismodel "/>
+      <sheetName val="Template informatiebehoefte - A"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Chevy Susanto" id="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" userId="S::chevy.susanto@nictiz.nl::4e93d0cc-e599-42c6-82b7-6ffb715c7e27" providerId="AD"/>
@@ -2779,58 +2662,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}" name="Tabel2" displayName="Tabel2" ref="A2:F13" totalsRowShown="0">
-  <autoFilter ref="A2:F13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{DAF348AE-F547-4357-9E3C-18B833059F60}" name="Invulling (zelf beschreven op basis van openEHR, FHIR R4 en EHDS LIM)" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6782DEBA-8C39-4E2C-BBC2-2CD68FCA1048}" name="Bronnen" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
-    <tableColumn id="6" xr3:uid="{1CF171A1-4997-44CE-A155-D2A5B879A058}" name="a.d.h.v. keuze OpenEHR als basismodel"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="6"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A2:N53" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
     <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D40E6C54-E02A-43EF-B5CE-2ED10C0E81CC}" name="Tabel4" displayName="Tabel4" ref="A1:B10" totalsRowShown="0">
   <autoFilter ref="A1:B10" xr:uid="{D40E6C54-E02A-43EF-B5CE-2ED10C0E81CC}"/>
   <tableColumns count="2">
@@ -2841,7 +2709,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E9" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B3:E9" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
   <tableColumns count="4">
@@ -3240,225 +3108,170 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E1B5B8-C013-4DD1-9595-10AFF6D9F062}">
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="62.33203125" customWidth="1"/>
-    <col min="3" max="3" width="76.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.5546875" customWidth="1"/>
-    <col min="6" max="6" width="64.109375" customWidth="1"/>
-    <col min="7" max="7" width="129.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="190.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="190.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+    </row>
+    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B4" s="38" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="219.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C4" s="39"/>
+      <c r="D4" s="40"/>
+    </row>
+    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B5" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
+    </row>
+    <row r="6" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
+    </row>
+    <row r="7" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="165" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C8" s="39"/>
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C9" s="39"/>
+      <c r="D9" s="41"/>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B10" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="360" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="216" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="7"/>
+      <c r="B11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="40"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="5"/>
+      <c r="C14" s="44"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="5"/>
+      <c r="C15" s="44"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="43"/>
+      <c r="C18" s="39"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="39"/>
+      <c r="C21" s="44"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="43"/>
+      <c r="C24" s="39"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1" display="https://www.hl7.org/fhir/R4/condition.html" xr:uid="{6169B330-2124-4ACC-9C33-24AFE1D4848F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3476,154 +3289,154 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3719,122 +3532,122 @@
     <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>84</v>
+        <v>51</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>89</v>
+        <v>56</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="19"/>
+        <v>63</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="17"/>
       <c r="D3" s="1" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
       <c r="I4" s="3" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="M4" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="N4" s="21"/>
-      <c r="O4" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="N4" s="19"/>
+      <c r="O4" s="8"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>107</v>
+      <c r="A5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3844,25 +3657,25 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
-        <v>112</v>
+      <c r="A6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3872,25 +3685,25 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
-        <v>107</v>
+      <c r="A7" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3900,25 +3713,25 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
-        <v>308</v>
+      <c r="A8" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -3928,15 +3741,15 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="C9" s="7"/>
       <c r="D9" s="3" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -3949,243 +3762,243 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
-        <v>119</v>
+      <c r="A10" s="19" t="s">
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>123</v>
+      <c r="A11" s="19" t="s">
+        <v>92</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="C12" s="10"/>
+      <c r="A12" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="9"/>
       <c r="D12" s="3" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>130</v>
+        <v>327</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>131</v>
+      <c r="A13" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
-        <v>137</v>
+      <c r="A14" s="19" t="s">
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>142</v>
+      <c r="A15" s="19" t="s">
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>339</v>
+      <c r="A16" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>366</v>
+        <v>309</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>334</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>367</v>
+      <c r="A17" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>335</v>
       </c>
       <c r="C17" s="3"/>
       <c r="F17" s="3"/>
@@ -4199,59 +4012,59 @@
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
-        <v>147</v>
+      <c r="A18" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="34" t="s">
-        <v>152</v>
+        <v>120</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
-        <v>153</v>
+      <c r="A19" s="19" t="s">
+        <v>122</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -4261,15 +4074,15 @@
       <c r="N19" s="3"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>156</v>
+      <c r="A20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -4282,57 +4095,57 @@
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
-        <v>162</v>
+      <c r="A21" s="19" t="s">
+        <v>131</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>383</v>
+        <v>350</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>351</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>165</v>
+      <c r="A22" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>384</v>
+        <v>132</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>352</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -4342,182 +4155,182 @@
       <c r="N22" s="3"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="C23" s="10"/>
+      <c r="A23" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="9"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="25"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="39"/>
+      <c r="L23" s="36"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
+      <c r="A24" s="8"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="25" t="s">
-        <v>380</v>
+      <c r="C24" s="23" t="s">
+        <v>348</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>169</v>
+        <v>318</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="L24" s="39" t="s">
-        <v>351</v>
+        <v>320</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>319</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>346</v>
+      <c r="A25" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="39" t="s">
-        <v>348</v>
+      <c r="C25" s="36" t="s">
+        <v>316</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="25"/>
+      <c r="J25" s="23"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="C26" s="10"/>
+      <c r="A26" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="9"/>
       <c r="D26" s="3" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="24"/>
+      <c r="A27" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="22"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
     <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
-        <v>180</v>
+      <c r="A28" s="19" t="s">
+        <v>149</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I28" s="3"/>
       <c r="N28" s="3"/>
     </row>
     <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>184</v>
+      <c r="A29" s="19" t="s">
+        <v>153</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -4527,25 +4340,25 @@
       <c r="N29" s="3"/>
     </row>
     <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
-        <v>188</v>
+      <c r="A30" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -4555,25 +4368,25 @@
       <c r="N30" s="3"/>
     </row>
     <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
-        <v>193</v>
+      <c r="A31" s="19" t="s">
+        <v>162</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -4583,105 +4396,105 @@
       <c r="N31" s="3"/>
     </row>
     <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C32" s="10"/>
+      <c r="A32" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="9"/>
       <c r="D32" s="3" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="s">
-        <v>204</v>
+      <c r="A33" s="19" t="s">
+        <v>173</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="N33" s="3"/>
     </row>
     <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
-        <v>207</v>
+      <c r="A34" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="33"/>
+      <c r="J34" s="31"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
     <row r="35" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
-        <v>211</v>
+      <c r="A35" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -4691,26 +4504,26 @@
       <c r="N35" s="3"/>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="10"/>
+      <c r="A36" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="9"/>
       <c r="D36" s="3" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -4718,53 +4531,53 @@
       <c r="N36" s="3"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
-        <v>218</v>
+      <c r="A37" s="19" t="s">
+        <v>187</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="s">
-        <v>222</v>
+      <c r="A38" s="19" t="s">
+        <v>191</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -4774,20 +4587,20 @@
       <c r="N38" s="3"/>
     </row>
     <row r="39" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
-        <v>226</v>
+      <c r="A39" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>228</v>
+      <c r="C39" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>197</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -4797,31 +4610,31 @@
       <c r="N39" s="3"/>
     </row>
     <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="10"/>
+      <c r="A40" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="9"/>
       <c r="D40" s="3" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>233</v>
+        <v>201</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>202</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -4829,31 +4642,31 @@
       <c r="N40" s="3"/>
     </row>
     <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C41" s="10"/>
+      <c r="A41" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="9"/>
       <c r="D41" s="3" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I41" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="J41" s="35" t="s">
-        <v>239</v>
+        <v>79</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="J41" s="33" t="s">
+        <v>208</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
@@ -4861,33 +4674,33 @@
       <c r="N41" s="3"/>
     </row>
     <row r="42" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C42" s="10"/>
+      <c r="A42" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="9"/>
       <c r="D42" s="3" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -4895,31 +4708,31 @@
       <c r="N42" s="3"/>
     </row>
     <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="C43" s="10"/>
+      <c r="A43" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="9"/>
       <c r="D43" s="3" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4927,22 +4740,22 @@
       <c r="N43" s="3"/>
     </row>
     <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
-        <v>253</v>
+      <c r="A44" s="19" t="s">
+        <v>222</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -4952,22 +4765,22 @@
       <c r="N44" s="3"/>
     </row>
     <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
-        <v>256</v>
+      <c r="A45" s="19" t="s">
+        <v>225</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4977,31 +4790,31 @@
       <c r="N45" s="3"/>
     </row>
     <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="C46" s="10"/>
+      <c r="A46" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="9"/>
       <c r="D46" s="3" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="J46" s="26" t="s">
-        <v>264</v>
+        <v>232</v>
+      </c>
+      <c r="J46" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -5009,111 +4822,111 @@
       <c r="N46" s="3"/>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C47" s="10"/>
+      <c r="A47" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="9"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="26"/>
+      <c r="J47" s="24"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="22" t="s">
-        <v>268</v>
+      <c r="A48" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="20" t="s">
+        <v>237</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J48" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="K48" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
+        <v>240</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="K48" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="L48" s="25"/>
+      <c r="M48" s="25"/>
       <c r="N48" s="3"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
-        <v>274</v>
+      <c r="A49" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="B49" s="3"/>
-      <c r="C49" s="22" t="s">
-        <v>275</v>
+      <c r="C49" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>277</v>
+        <v>245</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
       <c r="N49" s="3"/>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C50" s="10"/>
+      <c r="A50" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I50" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="J50" s="22" t="s">
-        <v>283</v>
+        <v>79</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>252</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -5121,31 +4934,31 @@
       <c r="N50" s="3"/>
     </row>
     <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C51" s="10"/>
+      <c r="A51" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="9"/>
       <c r="D51" s="3" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -5153,31 +4966,31 @@
       <c r="N51" s="3"/>
     </row>
     <row r="52" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="29"/>
+      <c r="A52" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="27"/>
       <c r="D52" s="3" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
@@ -5185,39 +4998,39 @@
       <c r="N52" s="3"/>
     </row>
     <row r="53" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
-        <v>295</v>
+      <c r="A53" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="B53" t="s">
-        <v>296</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>297</v>
+        <v>265</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>266</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="H53" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="I53" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="J53" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
     </row>
     <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="31"/>
-      <c r="C58" s="32"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="30"/>
     </row>
     <row r="59" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -5246,48 +5059,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5304,7 +5117,7 @@
     <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5324,23 +5137,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5363,61 +5176,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="B2" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>315</v>
+      <c r="B3" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="E4" s="14"/>
+      <c r="B4" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="E5" s="14"/>
+      <c r="B5" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="3" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>323</v>
+        <v>291</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>292</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5426,38 +5239,38 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="E7" s="14"/>
+      <c r="B7" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>329</v>
+      <c r="B8" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B9" s="14"/>
-      <c r="C9" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="E9" s="25"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5468,6 +5281,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5674,15 +5496,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5695,6 +5508,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5713,14 +5534,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichalCiszewski\Documents\Github\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455916BA-1B1A-461D-977E-85F4A305936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE709FF9-2A2B-4051-BB1C-831A73854CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,6 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={FC56F738-FB65-495B-9B48-E0F47216F010}</author>
     <author>tc={903FD87C-9891-4AE1-9361-7224FCD06B01}</author>
     <author>tc={B3533A99-0CB6-4646-9417-20A66FEFD573}</author>
     <author>tc={20B2A504-5F6F-4996-9921-E2104F9548D8}</author>
@@ -61,15 +60,7 @@
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
-      </text>
-    </comment>
-    <comment ref="J21" authorId="1" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -81,7 +72,7 @@
  evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="2" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <comment ref="K20" authorId="1" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -91,7 +82,7 @@
 Kortere waardelijst</t>
       </text>
     </comment>
-    <comment ref="K26" authorId="3" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+    <comment ref="K25" authorId="2" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -99,7 +90,7 @@
     Wel in metadata!</t>
       </text>
     </comment>
-    <comment ref="E29" authorId="4" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="E28" authorId="3" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -107,7 +98,7 @@
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="5" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B30" authorId="4" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -115,7 +106,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="6" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C30" authorId="5" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -123,7 +114,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="7" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C38" authorId="6" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="350">
   <si>
     <t>Veld</t>
   </si>
@@ -328,12 +319,6 @@
     <t>Opmerking</t>
   </si>
   <si>
-    <t>[Nummer van de informatie-requirement start bij 1, sub behoeftes kunnen worden gemodelleerd met X.X of X.X.X]</t>
-  </si>
-  <si>
-    <t>[Naam waaraan de informatie-requirement te herkennen is]</t>
-  </si>
-  <si>
     <t>[Geef hier een tekstuele omschrijving van de behoefte die ingevuld wordt met de informatie-requirement]</t>
   </si>
   <si>
@@ -341,9 +326,6 @@
   </si>
   <si>
     <t>[Geef aan in welke situaties het element waarmee de informatie-requirement gedekt wordt er zou moeten zijn, en evt. wanneer het afwezig kan zijn]</t>
-  </si>
-  <si>
-    <t>[Geef aan of de informatie relevant is voor gebruik van het model voor zaken in het verleden, in het heden, en/of de toekomst. Vaak is slechts een van deze situaties in scope van het bouwblok, maar niet altijd]</t>
   </si>
   <si>
     <t>[Geef aan waar de behoefte vandaan komt, bv. een specifieke informatiestandaard of bepaalde zorgrichtlijn]</t>
@@ -1370,7 +1352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1393,13 +1375,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1610,20 +1585,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1635,27 +1610,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1664,53 +1638,56 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1719,13 +1696,10 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2676,8 +2650,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N53" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:N53" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N52" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:N52" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
@@ -3039,34 +3013,31 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
-    <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
-  </threadedComment>
-  <threadedComment ref="J21" dT="2026-07-16T05:50:21.33" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
+  <threadedComment ref="J20" dT="2026-07-16T05:50:21.33" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
     <text> active
  inactive
  resolved
  in remission
  evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</text>
   </threadedComment>
-  <threadedComment ref="K21" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+  <threadedComment ref="K20" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
     <text>1. Actief
 2. Inactief
 Kortere waardelijst</text>
   </threadedComment>
-  <threadedComment ref="K26" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+  <threadedComment ref="K25" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
     <text>Wel in metadata!</text>
   </threadedComment>
-  <threadedComment ref="E29" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+  <threadedComment ref="E28" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
   </threadedComment>
-  <threadedComment ref="B31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+  <threadedComment ref="B30" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+  <threadedComment ref="C30" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C39" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C38" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
   </threadedComment>
 </ThreadedComments>
@@ -3131,143 +3102,143 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="39"/>
     </row>
     <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
     </row>
     <row r="6" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="41"/>
+      <c r="D7" s="40"/>
     </row>
     <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="41"/>
     </row>
     <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="41"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="40"/>
     </row>
     <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
+        <v>295</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="43"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="40"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44"/>
+      <c r="C14" s="43"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
-      <c r="C15" s="44"/>
+      <c r="C15" s="43"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="43"/>
-      <c r="C18" s="39"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="38"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="39"/>
-      <c r="C21" s="44"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="43"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="43"/>
-      <c r="C24" s="39"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3318,7 +3289,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -3431,7 +3402,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -3511,7 +3482,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -3574,80 +3545,84 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>63</v>
+    <row r="3" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3" s="17"/>
-      <c r="D3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="J3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="3" t="s">
+      <c r="K3" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="N3" s="18"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="D4" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3656,26 +3631,26 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>80</v>
+    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>81</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3684,26 +3659,26 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>84</v>
+    <row r="7" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="s">
-        <v>76</v>
+        <v>274</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>325</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3712,27 +3687,20 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
-        <v>277</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="7"/>
       <c r="D8" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>328</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3740,332 +3708,332 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>88</v>
-      </c>
+    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
-        <v>93</v>
-      </c>
+    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="9"/>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>328</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="L11" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="9"/>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>98</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>322</v>
+        <v>71</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>100</v>
+    <row r="13" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>106</v>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>326</v>
+        <v>76</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>306</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
-        <v>111</v>
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>304</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>317</v>
+        <v>306</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>331</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>114</v>
+        <v>310</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>74</v>
+        <v>307</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>307</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
-        <v>116</v>
+    <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>336</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>118</v>
+        <v>338</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
-        <v>339</v>
-      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -4073,264 +4041,271 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="D20" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>131</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>351</v>
+        <v>129</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>349</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K21" s="3" t="s">
         <v>130</v>
       </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="3" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="B22" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="22"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="35"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="36"/>
+      <c r="K23" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="L23" s="35" t="s">
+        <v>316</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="23" t="s">
-        <v>348</v>
+      <c r="C24" s="35" t="s">
+        <v>313</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J24" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="K24" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="36" t="s">
-        <v>319</v>
-      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="36" t="s">
-        <v>316</v>
-      </c>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C25" s="9"/>
       <c r="D25" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="3" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="B26" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="F27" s="3"/>
+    <row r="27" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
-        <v>149</v>
+    <row r="28" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
-        <v>153</v>
+    <row r="29" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -4339,26 +4314,26 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>157</v>
+    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
+        <v>159</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -4367,65 +4342,60 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3" t="s">
+    <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>163</v>
       </c>
+      <c r="B31" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="9"/>
       <c r="D31" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="9"/>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="D32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
+    <row r="33" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
         <v>173</v>
       </c>
       <c r="B33" s="3"/>
@@ -4436,148 +4406,148 @@
         <v>175</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>176</v>
+    <row r="34" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>177</v>
+        <v>337</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>123</v>
+        <v>338</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="31"/>
+      <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" s="9"/>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="D36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J36" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="K36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>187</v>
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
+        <v>188</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
-        <v>191</v>
+    <row r="38" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="C38" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="D38" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>194</v>
+        <v>93</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -4586,121 +4556,130 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="34" t="s">
+      <c r="B39" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="C39" s="9"/>
+      <c r="D39" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="E39" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>199</v>
+      </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
-        <v>198</v>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
+        <v>200</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>202</v>
+        <v>76</v>
+      </c>
+      <c r="I40" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="J40" s="32" t="s">
+        <v>205</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
-        <v>203</v>
+    <row r="41" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="18" t="s">
+        <v>206</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G41" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="H41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="J41" s="33" t="s">
-        <v>208</v>
+        <v>76</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
-        <v>209</v>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>213</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>213</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -4708,39 +4687,32 @@
       <c r="N42" s="3"/>
     </row>
     <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" s="9"/>
+      <c r="A43" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="D43" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
     <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="18" t="s">
         <v>222</v>
       </c>
       <c r="B44" s="3"/>
@@ -4751,11 +4723,11 @@
         <v>224</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -4764,276 +4736,251 @@
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19" t="s">
+    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3" t="s">
+      <c r="B45" s="9" t="s">
         <v>226</v>
       </c>
+      <c r="C45" s="9"/>
       <c r="D45" s="3" t="s">
         <v>227</v>
       </c>
+      <c r="E45" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="F45" s="3" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J45" s="23" t="s">
+        <v>230</v>
+      </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="19" t="s">
-        <v>228</v>
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C46" s="9"/>
-      <c r="D46" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>91</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J46" s="24" t="s">
-        <v>233</v>
-      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="23"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="D47" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="F47" s="3"/>
+      <c r="E47" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
+      <c r="H47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="K47" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="20" t="s">
-        <v>237</v>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="19" t="s">
+        <v>241</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J48" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="K48" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="L48" s="25"/>
-      <c r="M48" s="25"/>
+        <v>176</v>
+      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="20" t="s">
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="18" t="s">
         <v>244</v>
       </c>
+      <c r="B49" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C49" s="9"/>
       <c r="D49" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E49" s="9" t="s">
         <v>246</v>
       </c>
+      <c r="E49" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="F49" s="3" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="19" t="s">
-        <v>247</v>
+      <c r="A50" s="18" t="s">
+        <v>250</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I50" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="J50" s="20" t="s">
-        <v>252</v>
+        <v>76</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C51" s="9"/>
+    <row r="51" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="26"/>
       <c r="D51" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
     </row>
-    <row r="52" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" s="27"/>
-      <c r="D52" s="3" t="s">
+    <row r="52" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
         <v>261</v>
       </c>
+      <c r="B52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>263</v>
+      </c>
       <c r="E52" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B53" t="s">
+      <c r="H52" t="s">
         <v>265</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="I52" t="s">
         <v>266</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="J52" t="s">
         <v>267</v>
       </c>
-      <c r="H53" t="s">
-        <v>268</v>
-      </c>
-      <c r="I53" t="s">
-        <v>269</v>
-      </c>
-      <c r="J53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+    </row>
+    <row r="57" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-    </row>
-    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="29"/>
-      <c r="C58" s="30"/>
-    </row>
-    <row r="59" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
+      <c r="C57" s="29"/>
+    </row>
+    <row r="58" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5059,10 +5006,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>50</v>
@@ -5082,25 +5029,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5117,7 +5064,7 @@
     <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5137,7 +5084,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B1" t="s">
         <v>22</v>
@@ -5145,15 +5092,15 @@
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5177,7 +5124,7 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -5185,52 +5132,52 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D6" s="19" t="s">
         <v>289</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>292</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5240,37 +5187,37 @@
     </row>
     <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>291</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>294</v>
       </c>
       <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="35" t="s">
-        <v>295</v>
+      <c r="D8" s="34" t="s">
+        <v>292</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B9" s="13"/>
       <c r="C9" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="23"/>
+        <v>309</v>
+      </c>
+      <c r="E9" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5281,12 +5228,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5497,20 +5446,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5535,12 +5485,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichalCiszewski\Documents\Github\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/eduard_derijcke_nictiz_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE709FF9-2A2B-4051-BB1C-831A73854CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8B207D1-1355-40B1-8598-1BBE603C0CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
-    <sheet name="Concept" sheetId="9" r:id="rId2"/>
+    <sheet name="Concept" sheetId="2" r:id="rId2"/>
     <sheet name="Bronnen" sheetId="6" r:id="rId3"/>
     <sheet name="Informatiebehoefte" sheetId="1" r:id="rId4"/>
     <sheet name="Ongedekte informatiebehoefte" sheetId="3" r:id="rId5"/>
@@ -22,12 +22,6 @@
     <sheet name="Basismodel" sheetId="7" r:id="rId7"/>
     <sheet name="Ter discussie" sheetId="8" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="Informatiebron">[1]!Tabel3[Naam bron]</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +45,25 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={903FD87C-9891-4AE1-9361-7224FCD06B01}</author>
+    <author>tc={CD16CA43-E215-4DCF-A4C0-2D380EB1C0BC}</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{CD16CA43-E215-4DCF-A4C0-2D380EB1C0BC}">
+      <text>
+        <t xml:space="preserve">[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
+    Uit Scope en Usage van Condition FHIR R4 v4.0.1 </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FC56F738-FB65-495B-9B48-E0F47216F010}</author>
     <author>tc={B3533A99-0CB6-4646-9417-20A66FEFD573}</author>
     <author>tc={20B2A504-5F6F-4996-9921-E2104F9548D8}</author>
     <author>tc={DC3A08E9-01DD-48D1-B7F5-357810DE5428}</author>
@@ -60,65 +72,61 @@
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-     active
- inactive
- resolved
- in remission
- evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</t>
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
+    AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
       </text>
     </comment>
-    <comment ref="K20" authorId="1" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <comment ref="K21" authorId="1" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     1. Actief
 2. Inactief
 Kortere waardelijst</t>
       </text>
     </comment>
-    <comment ref="K25" authorId="2" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+    <comment ref="K27" authorId="2" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     Wel in metadata!</t>
       </text>
     </comment>
-    <comment ref="E28" authorId="3" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="E30" authorId="3" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B30" authorId="4" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B32" authorId="4" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C30" authorId="5" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C32" authorId="5" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C38" authorId="6" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C40" authorId="6" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Opmerkingenthread]
+U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
+Opmerking:
     ter discussie</t>
       </text>
     </comment>
@@ -127,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="394">
   <si>
     <t>Veld</t>
   </si>
@@ -135,53 +143,81 @@
     <t>Beschrijving</t>
   </si>
   <si>
+    <t>a.d.h.v. keuze FHIR als basismodel</t>
+  </si>
+  <si>
     <t>Conceptbeschrijving</t>
   </si>
   <si>
-    <t>Een conditie beschrijft een klinisch relevante gezondheidstoestand, diagnose, probleem, aandoening of andere gezondheidsituatie die betrekking heeft op de gezondheid en/of het welzijn van de patiënt. Deze toestand kan benoemd zijn door de patiënt, gerelateerd persoon of door de zorgverlener. De gezondheidstoestand kan aanleiding geven tot behandeling, monitoring of vervolgbeleid.</t>
+    <t>[De definitie of beschrijving van het concept.]</t>
+  </si>
+  <si>
+    <t>Een klinische aandoening, probleem, diagnose of andere gebeurtenis, situatie, kwestie of klinisch concept dat aanleiding geeft tot zorg.</t>
   </si>
   <si>
     <t>Doel</t>
   </si>
   <si>
-    <t xml:space="preserve">Een overzicht van gezondheidstoestanden/diagnoses/aandoeningen van de patient. </t>
+    <t>[De doelen en redenen om het concept vast te leggen en/of uit te wisselen.]</t>
+  </si>
+  <si>
+    <t>Het doel van het concept is het eenduidig vastleggen en uitwisselen van een klinisch relevante diagnose, aandoening, gezondheidstoestand of ander zorgpunt van een patiënt. Dit ondersteunt nader onderzoek, behandeling, monitoring en overdracht van zorg, ook wanneer het gaat om een niet-negatieve gezondheidstoestand, zoals zwangerschap, of om een toestand die het gevolg is van een eerdere ingreep.</t>
   </si>
   <si>
     <t>Gebruiksscenario(’s)</t>
   </si>
   <si>
-    <t>Een overzicht van gezondheidstoestanden/diagnoses/aandoeningen van de patient. Het wordt gebruikt in de informatiestandaarden BgZ-MSZ, Eerstelijnszorg, .. 
-Conditie kan worden gebruikt om het gezondheidsprobleem in een zorgepisode te duiden.</t>
+    <t>[Geeft aan in welke context(en) het concept wordt gebruikt. Geef voorbeelden van gebruik in informatiestandaarden.]</t>
+  </si>
+  <si>
+    <t>Het kan worden gebruikt om informatie vast te leggen over een ziekte of aandoening die is vastgesteld op basis van klinische redenering over pathologische en pathofysiologische bevindingen (diagnose); over gezondheidsproblemen of -situaties die een zorgverlener als schadelijk of potentieel schadelijk beschouwt en die nader onderzoek en behandeling vereisen (probleem); of over andere gezondheidsproblemen of -situaties die mogelijk voortdurende monitoring en/of behandeling behoeven (gezondheidsprobleem/-zorgpunt).
+De 'Condition'-resource kan worden gebruikt om een ​​bepaalde gezondheidstoestand van een patiënt vast te leggen die doorgaans niet als een negatieve uitkomst wordt beschouwd, zoals zwangerschap. De 'Condition'-resource kan ook worden gebruikt om een ​​aandoening of toestand vast te leggen die volgt op een ingreep, zoals de status van 'onderbeenamputatiepatiënt' na een amputatieprocedure.
+Spoedsamenvatting 2.2.0, bij het opstellen van de episodes en problemen 
+BgZ-MSZ: bij klachten en diagnoses
+eOverdracht: problemen
+Eerstelijnszorg: problemen</t>
   </si>
   <si>
     <t>Representatie</t>
   </si>
   <si>
-    <t>Een gezondheidsstoestand heeft een start en kan een einddatum hebben, maar hoeft niet. Het kan gevlagt zijn om in de probleemlijst van de patient aanwezig te blijven, ook al is de gezondheidsstoestand opgeheven.</t>
+    <t>[Beschrijf hier wat er voor de dossiervorming belangrijk is rondom de levenscyclus en instantiaties van het concept.]</t>
+  </si>
+  <si>
+    <t>Een instantiatie beschrijft één klinisch relevante conditie bij een patiënt. Veranderingen in status of zekerheid worden in dezelfde registratie bijgewerkt; voor een andere conditie of afzonderlijke episode wordt een nieuwe instantiatie gemaakt. Beëindigde of weerlegde condities blijven als historie beschikbaar.</t>
   </si>
   <si>
     <t>Alias(sen)</t>
   </si>
   <si>
+    <t>[Alle bekende synoniemen voor het concept.]</t>
+  </si>
+  <si>
     <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening)</t>
   </si>
   <si>
     <t>Juist gebruik</t>
   </si>
   <si>
-    <t>Voor het vastleggen van diagnoses, probleem, en andere situaties van de patiënt die geen negatieve uitkomst hebben. zoals een zwangerschap.</t>
+    <t>[Beschrijf hier waarvoor het concept wél bedoeld is].</t>
+  </si>
+  <si>
+    <t>Het concept is bedoeld voor het vastleggen van een klinisch relevante aandoening, diagnose, probleem, gezondheidstoestand, risico of zorgpunt dat beoordeling, behandeling of monitoring vereist.</t>
   </si>
   <si>
     <t>Onjuist gebruik</t>
   </si>
   <si>
-    <t>Het wordt niet gebruikt om de functionele status, bijvoorbeeld vermogen tot ADL, vast te leggen. Het wordt niet gebruikt voor symptomen die je observeert of uitvraagt, met andere woorden wanneer een symptoom bijdraagt aan de aandoening, dient het niet opgenomen te worden als condition.</t>
+    <t>[Beschrijf hier waar het concept niet voor bedoeld is, en geef waar mogelijk aan welk concept er wel geschikt voor is.]</t>
+  </si>
+  <si>
+    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
   </si>
   <si>
     <t>Referenties</t>
   </si>
   <si>
-    <t>EHDS LIM EHDSCondition v1.0.0; FHIR R4 resource Condition; openEHR Problem/Diagnosis 1.5.0</t>
+    <t>[Relevante bronstandaarden of informatiebronnen die het ontwerp en de scope van het concept hebben beïnvloed.]</t>
   </si>
   <si>
     <t>Condition - FHIR v4.0.1</t>
@@ -190,6 +226,18 @@
     <t>ART-DECOR-id</t>
   </si>
   <si>
+    <t>[Het id op ART-DECOR van het afsprakenmodel, bv 2.16.840.1.113883.2.4.3.11.60.153.4.12/2026-06-04T00:00:00]</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.4.3.11.60.153.4.30/2026-07-29T00:00:00</t>
+  </si>
+  <si>
+    <t>Keuze Basismodel</t>
+  </si>
+  <si>
+    <t>Concept-sheet is opgemaakt met spelregel: https://nictiz.atlassian.net/browse/DAGIM-72</t>
+  </si>
+  <si>
     <t>Type bron</t>
   </si>
   <si>
@@ -217,6 +265,10 @@
     <t>Ja</t>
   </si>
   <si>
+    <t>Condition model - EHDS Logical Information Models v1.0.0
+https://health.ec.europa.eu/publications/ehn-guideline-patient-summary_en</t>
+  </si>
+  <si>
     <t>FHIR R4 resource Condition</t>
   </si>
   <si>
@@ -277,6 +329,10 @@
     <t>Volgens de DoD Q3 moet dit opgenomen worden in deze iteratie van de GBB</t>
   </si>
   <si>
+    <t>https://referentiemodel.nhg.org/
+https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf</t>
+  </si>
+  <si>
     <t>Nummer</t>
   </si>
   <si>
@@ -319,6 +375,12 @@
     <t>Opmerking</t>
   </si>
   <si>
+    <t>[Nummer van de informatie-requirement start bij 1, sub behoeftes kunnen worden gemodelleerd met X.X of X.X.X]</t>
+  </si>
+  <si>
+    <t>[Naam waaraan de informatie-requirement te herkennen is]</t>
+  </si>
+  <si>
     <t>[Geef hier een tekstuele omschrijving van de behoefte die ingevuld wordt met de informatie-requirement]</t>
   </si>
   <si>
@@ -328,6 +390,9 @@
     <t>[Geef aan in welke situaties het element waarmee de informatie-requirement gedekt wordt er zou moeten zijn, en evt. wanneer het afwezig kan zijn]</t>
   </si>
   <si>
+    <t>[Geef aan of de informatie relevant is voor gebruik van het model voor zaken in het verleden, in het heden, en/of de toekomst. Vaak is slechts een van deze situaties in scope van het bouwblok, maar niet altijd]</t>
+  </si>
+  <si>
     <t>[Geef aan waar de behoefte vandaan komt, bv. een specifieke informatiestandaard of bepaalde zorgrichtlijn]</t>
   </si>
   <si>
@@ -341,835 +406,128 @@
   </si>
   <si>
     <t>Ja (Reference model: subject of care) 1:1</t>
-  </si>
-  <si>
-    <t>Nee</t>
-  </si>
-  <si>
-    <t>CON-1.1</t>
-  </si>
-  <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>Verwijzing naar Patient</t>
-  </si>
-  <si>
-    <t>1..1</t>
-  </si>
-  <si>
-    <t>EHDS LIM EHDSCondition 1.0.0</t>
-  </si>
-  <si>
-    <t>CON-1.2</t>
-  </si>
-  <si>
-    <t>Subject of care</t>
-  </si>
-  <si>
-    <t>Vewijzing naar Subject of Care</t>
-  </si>
-  <si>
-    <t>openEHR Problem/Diagnosis 1.7.4</t>
-  </si>
-  <si>
-    <t>CON-1.3</t>
-  </si>
-  <si>
-    <t>CON-2</t>
-  </si>
-  <si>
-    <t>Ja (identifier)</t>
-  </si>
-  <si>
-    <t>Ja (architype.id) maar komt niet voor in de archetypen, maar komt naar voren bij het opslaan (originating_system_item_ids : DV_IDENTIFIER). is 0..*</t>
-  </si>
-  <si>
-    <t>CON-2.1</t>
-  </si>
-  <si>
-    <t>header.identifier</t>
-  </si>
-  <si>
-    <t>Business identifier van het object</t>
-  </si>
-  <si>
-    <t>0..*</t>
-  </si>
-  <si>
-    <t>CON-2.2</t>
-  </si>
-  <si>
-    <t>Identificatie</t>
-  </si>
-  <si>
-    <t>Unieke identificatie van één specifieke episode. De unieke identificatie wordt gebruikt om één specifieke episode te herkennen binnen een lijst met alle episodes van een patiënt.</t>
-  </si>
-  <si>
-    <t>1..*</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0</t>
-  </si>
-  <si>
-    <t>CON-3</t>
-  </si>
-  <si>
-    <t>0..* Choice of types</t>
-  </si>
-  <si>
-    <t>Ja (RM:other_participations)</t>
-  </si>
-  <si>
-    <t>CON-3.1</t>
-  </si>
-  <si>
-    <t>zorgverlener als auteur</t>
-  </si>
-  <si>
-    <t>authorEHDSHealthProfessional</t>
-  </si>
-  <si>
-    <t>Verwijziging naar EHDSHealthProfessional</t>
-  </si>
-  <si>
-    <t>Ja (recorder = Practitioner of PractitionerRole)</t>
-  </si>
-  <si>
-    <t>ja</t>
-  </si>
-  <si>
-    <t>CON-3.2</t>
-  </si>
-  <si>
-    <t>organisatie als auteur</t>
-  </si>
-  <si>
-    <t>authorEHDSOrganisation</t>
-  </si>
-  <si>
-    <t>Verwijziging naar EHDSOrganization</t>
-  </si>
-  <si>
-    <t>Ja (recorder.PracticionerRole.Organisation)</t>
-  </si>
-  <si>
-    <t>CON-3.3</t>
-  </si>
-  <si>
-    <t>apparaat als auteur</t>
-  </si>
-  <si>
-    <t>authorEHDSDevice</t>
-  </si>
-  <si>
-    <t>Verwijziging naar EHDSDevice</t>
-  </si>
-  <si>
-    <t>CON-4</t>
-  </si>
-  <si>
-    <t>CON-4.1</t>
-  </si>
-  <si>
-    <t>header.date</t>
-  </si>
-  <si>
-    <t>DatumTijd</t>
-  </si>
-  <si>
-    <t>0..1</t>
-  </si>
-  <si>
-    <t>Ja (recordedDate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ja. Opmerking Wouter bij AllergieIntolerantie: metadata komt in elk archetype voor. </t>
-  </si>
-  <si>
-    <t>CON-4.2</t>
-  </si>
-  <si>
-    <t>Time Stamp</t>
-  </si>
-  <si>
-    <t>CON-5</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status van het object </t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Ja (clinicalStatus)</t>
-  </si>
-  <si>
-    <t>Ja  0..1 (status)</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemStatus</t>
-  </si>
-  <si>
-    <t>CON-5.1</t>
-  </si>
-  <si>
-    <t>De status is actief of open, danwel gesloten
-Zib 2017: De probleemstatus beschrijft de toestand van het probleem:
-Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
-Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0; Zib 2017; zib 2020</t>
-  </si>
-  <si>
-    <t>CON-5.2</t>
-  </si>
-  <si>
-    <t>CON-6</t>
-  </si>
-  <si>
-    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gecodeerde concept </t>
-  </si>
-  <si>
-    <t>Ja (Reference model: Information Provider) 0..1 Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software.</t>
-  </si>
-  <si>
-    <t>CON-7</t>
-  </si>
-  <si>
-    <t>De taal waarin het object is geschreven</t>
-  </si>
-  <si>
-    <t>Waardelijst BCP 47</t>
-  </si>
-  <si>
-    <t>Ja (language)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ja
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Opmerking Wouter bij AllergieIntolerantie: metadata komt in elk archetype voor. </t>
-    </r>
-  </si>
-  <si>
-    <t>CON-8</t>
-  </si>
-  <si>
-    <t>Naam van de conditie</t>
-  </si>
-  <si>
-    <t>Ja (code, 0..1)</t>
-  </si>
-  <si>
-    <t>Ja (Problem / Diagnosis name)</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemNaam</t>
-  </si>
-  <si>
-    <t>CON-8.1</t>
-  </si>
-  <si>
-    <t>problem</t>
-  </si>
-  <si>
-    <t>Code die de aandoening, het probleem of de diagnose identificeert</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): ICD-10, SNOMED CT, ICD-O, Orphacode if rare disease is diagnosed</t>
-  </si>
-  <si>
-    <t>CON-8.2</t>
-  </si>
-  <si>
-    <t>Problem/Diagnosis name</t>
-  </si>
-  <si>
-    <t>Identificatie van het probleem of de diagnose, met de naam erbij.
-Opmerking: Codering van de naam van het probleem of de diagnose met een terminologie heeft de voorkeur, indien mogelijk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String of waardelijst </t>
-  </si>
-  <si>
-    <t>CON-8.3</t>
-  </si>
-  <si>
-    <t>ProbleemNaam</t>
-  </si>
-  <si>
-    <t>De probleemnaam definieert het probleem. Afhankelijk van de setting kunnen verschillende codestelsels worden gebruikt. De ProbleemNaamCodelijst geeft een overzicht van de mogelijke codestelsels</t>
-  </si>
-  <si>
-    <t>Waardelijst (DHD Diagnosethesaurus; ICD-10, dutch translation; SNOMED CT; NANDA-I; ICF; ICPC-1 NL; DSM-IV; DSM-5; GGZ Diagnoselijst)</t>
-  </si>
-  <si>
-    <t>Zib 2017, zib 2020</t>
-  </si>
-  <si>
-    <t>CON-8.4</t>
-  </si>
-  <si>
-    <t>zorgepisodetitel</t>
-  </si>
-  <si>
-    <t>Beschrijving van het gezondheidsprobleem. Dit kan een door de zorgverlener geformuleerde tekst zijn, danwel de tekstuele omschrijving van de ICPC code.</t>
-  </si>
-  <si>
-    <t>Waardelijst (ICPC) + tekstuele omschrijving</t>
-  </si>
-  <si>
-    <t>CON-9</t>
-  </si>
-  <si>
-    <t>Begin datum van de conditie</t>
-  </si>
-  <si>
-    <t>De datum en evt. tijd waarop de conditie is begonnen</t>
-  </si>
-  <si>
-    <t>niet toekomst</t>
-  </si>
-  <si>
-    <t>Ja (onsetDateTime)</t>
-  </si>
-  <si>
-    <t>ja 0..1 Date/time of onset</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemBeginDatum</t>
-  </si>
-  <si>
-    <t>CON-9.1</t>
-  </si>
-  <si>
-    <t>onsetDate</t>
-  </si>
-  <si>
-    <t>De datum waarop de conditie/probleem is begonnen</t>
-  </si>
-  <si>
-    <t>CON-9.2</t>
-  </si>
-  <si>
-    <t>ProbleemBeginDatum</t>
-  </si>
-  <si>
-    <t>Begin van de aandoening, waarop het probleem betrekking heeft. Vooral bij klachten waarbij het langer duurt voordat de uiteindelijke diagnose gesteld wordt is het belangrijk niet alleen de diagnosedatum te weten, maar ook sinds wanneer de aandoening al bestaat. Een vage datum, bijv. alleen een jaartal of een maand en een jaartal, is toegestaan.</t>
-  </si>
-  <si>
-    <t>Zib 2017; zib 2020</t>
-  </si>
-  <si>
-    <t>CON-9.3</t>
-  </si>
-  <si>
-    <t>CON-10</t>
-  </si>
-  <si>
-    <t>Eind datum van de conditie</t>
-  </si>
-  <si>
-    <t>De datum en evt. tijd waarop de conditie is afgelopen</t>
-  </si>
-  <si>
-    <t>verleden</t>
-  </si>
-  <si>
-    <t>Ja (abatementDateTime)</t>
-  </si>
-  <si>
-    <t>ja 0..1 Date/time of resolution</t>
-  </si>
-  <si>
-    <t>CON-10.1</t>
-  </si>
-  <si>
-    <t>endDate</t>
-  </si>
-  <si>
-    <t>De datum of geschatte datum waarop de conditie in remissie ging of verdween</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemEindDatum</t>
-  </si>
-  <si>
-    <t>CON-10.2</t>
-  </si>
-  <si>
-    <t>ProbleemEindDatum</t>
-  </si>
-  <si>
-    <t>Datum waarop de aandoening, waarop het probleem betrekking heeft, als niet meer aanwezig wordt beschouwd. Deze datum hoeft niet gelijk te zijn aan de datum waarop de statuswijzinging van het probleem is vastgelegd. Een vage datum, bijv. alleen een jaartal of een maand en een jaartal, is toegestaan.</t>
-  </si>
-  <si>
-    <t>Usecase Spoedsamenvatting van Acute Zorg</t>
-  </si>
-  <si>
-    <t>CON-10.3</t>
-  </si>
-  <si>
-    <t>zorgepisode.Einddatum</t>
-  </si>
-  <si>
-    <t>Indien de episode als periode gedefinieerd wordt, moet de einddatum van de afsluiting van de zorgepisode worden ingegegeven.</t>
-  </si>
-  <si>
-    <t>CON-11</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Categorie(ën) van het probleem (bijv. POA - aanwezig bij opname, HAC - in het ziekenhuis opgelopen aandoening, en andere categorisaties)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. -&gt; WAAROM WIL JE DIT VELD HEBBEN - Bouchra stuurt een link van EHN guidelines?</t>
-    </r>
-  </si>
-  <si>
-    <t>Ja (category)</t>
-  </si>
-  <si>
-    <t>nee. Wouter vragen of dat via een cluster kan??</t>
-  </si>
-  <si>
-    <t>CON-12</t>
-  </si>
-  <si>
-    <t>resolutionCircumstances</t>
-  </si>
-  <si>
-    <t>Beschrijft de reden waarom de status van het probleem is veranderd van actueel naar inactief (bijv. chirurgische ingreep, medische behandeling, enz.).</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>Ja? (note.text)</t>
-  </si>
-  <si>
-    <t>Ja? Comment</t>
-  </si>
-  <si>
-    <t>CON-13</t>
-  </si>
-  <si>
-    <t>severity</t>
-  </si>
-  <si>
-    <t>Een subjectieve beoordeling van de ernst van de aandoening, zoals vastgesteld door de arts.</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): HL7 Condition/Diagnosis Severity; SNOMED CT</t>
-  </si>
-  <si>
-    <t>heden</t>
-  </si>
-  <si>
-    <t>Ja  (Severity)</t>
-  </si>
-  <si>
-    <t>Ja Severity (optional)</t>
-  </si>
-  <si>
-    <t>CON-14</t>
-  </si>
-  <si>
-    <t>bodySite</t>
-  </si>
-  <si>
-    <t>De anatomische locatie, inclusief de zijde waar deze aandoening zich manifesteert.</t>
-  </si>
-  <si>
-    <t>Verwijziging naar EHDSBodyStructure</t>
-  </si>
-  <si>
-    <t>Ja (bodySite)</t>
-  </si>
-  <si>
-    <t>Ja (StructuredBodySite)</t>
-  </si>
-  <si>
-    <t>CON-14.1</t>
-  </si>
-  <si>
-    <t>ProbleemAnatomischeLocatie</t>
-  </si>
-  <si>
-    <t>Anatomische locatie die de focus is van de verrichting.</t>
-  </si>
-  <si>
-    <t>CON-14.2</t>
-  </si>
-  <si>
-    <t>ProbleemLateraliteit</t>
-  </si>
-  <si>
-    <t>Lateraliteit verbijzondert de anatomische locatie door, indien van toepassing, de zijdigheid vast te leggen, bijvoorbeeld links.</t>
-  </si>
-  <si>
-    <t>CON-15</t>
-  </si>
-  <si>
-    <t>stage</t>
-  </si>
-  <si>
-    <t>Het stadium/de graad wordt doorgaans formeel beoordeeld aan de hand van een specifiek stadium-/gradatiesysteem. Er kunnen meerdere beoordelingssystemen worden gebruikt.</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): e.g. TNM, ICD-O-3, Bi-Rads, Li-Rads, …</t>
-  </si>
-  <si>
-    <t>Ja (stage)</t>
-  </si>
-  <si>
-    <t>Ja/Nee maar via extensie / uitbreiding van archetype Specific Details (cluster?) -&gt; Wouter vragen.</t>
-  </si>
-  <si>
-    <t>CON-16</t>
-  </si>
-  <si>
-    <t>Status van verificatie van de conditie</t>
-  </si>
-  <si>
-    <t>CON-16.1</t>
-  </si>
-  <si>
-    <t>diagnosisAssertionStatus</t>
-  </si>
-  <si>
-    <t>Een bewering over de zekerheid die aan een diagnose is verbonden. Diagnostisch en/of klinisch bewijs van een aandoening</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): HL7 Condition Verification Status</t>
-  </si>
-  <si>
-    <t>Ja (verificationStatus)</t>
-  </si>
-  <si>
-    <t>Ja? DiagnosticCertainty? proberbly, confermed, supsected</t>
-  </si>
-  <si>
-    <t>VerificatieStatus ZIB!</t>
-  </si>
-  <si>
-    <t>CON-P16.2</t>
-  </si>
-  <si>
-    <t>VerificatieStatus</t>
-  </si>
-  <si>
-    <t>Klinische status van het probleem of de diagnose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VerificatieStatusCodelijst </t>
-  </si>
-  <si>
-    <t>CON-17</t>
-  </si>
-  <si>
-    <t>specialistContact</t>
-  </si>
-  <si>
-    <t>Een zorgverlener die specifiek betrokken is bij het probleem, als voorkeurscontactpersoon.</t>
-  </si>
-  <si>
-    <t>Verwijzing naar de EHDSHealthProfessional</t>
-  </si>
-  <si>
-    <t>Ja note.text/careteam.reason</t>
-  </si>
-  <si>
-    <t>Onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is -&gt; Wouter vragen</t>
-  </si>
-  <si>
-    <t>CON-18</t>
-  </si>
-  <si>
-    <t>externalResource</t>
-  </si>
-  <si>
-    <t>Externe bronnen die specifiek betrekking hebben op het probleem, bijvoorbeeld een link naar een probleem met een zeldzame ziekte en de bijbehorende richtlijnen</t>
-  </si>
-  <si>
-    <t>uri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0..* </t>
-  </si>
-  <si>
-    <t>Ja(structureDefinition.extension:relatedArtifact) FMM2</t>
-  </si>
-  <si>
-    <t>ja/nee Guideline Identifier (focust op richtlijnen of breder, LIM is breder)</t>
-  </si>
-  <si>
-    <t>CON-19</t>
-  </si>
-  <si>
-    <t>Toelichting van diegene die het Probleem heeft vastgesteld of bijgewerkt.</t>
-  </si>
-  <si>
-    <t>Ja (note)</t>
-  </si>
-  <si>
-    <t>Ja (comment)</t>
-  </si>
-  <si>
-    <t>CON-20</t>
-  </si>
-  <si>
-    <t>NadereSpecificatieProbleemNaam</t>
-  </si>
-  <si>
-    <t>Wat is precies de behoefte van MBZ-MSZ voor een waardelijst als een naderespecificatie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String en waardelijst </t>
-  </si>
-  <si>
-    <t>Zib 2020; informatiestandaard BgZ-MSZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ja/nee (code.text) </t>
-  </si>
-  <si>
-    <t>Ja, variant (tekst or coded tekst)</t>
-  </si>
-  <si>
-    <t>Actie</t>
-  </si>
-  <si>
-    <t>Notitie</t>
-  </si>
-  <si>
-    <t>[Actie om te ondernemen, kies uit de 3 acties: cluster, andere bouwsteen en modelleren]</t>
-  </si>
-  <si>
-    <t>[Eventuele notitie]</t>
-  </si>
-  <si>
-    <t>[Naam van de informatie-requirement ]</t>
-  </si>
-  <si>
-    <t>In het FHIR profiel is er voor de referentie voor auteur.Device nog geen Device profiel toegevoegd omdat nlcore-device nog niet bestaat. Deze moet tzt wel toegevoegd worden.</t>
-  </si>
-  <si>
-    <t>Onderwerp</t>
-  </si>
-  <si>
-    <t>Potentiële basismodellen</t>
-  </si>
-  <si>
-    <t>FHIR R4 resource Condition
-openEHR archetype Problem/Diagnosis 1.7.3</t>
-  </si>
-  <si>
-    <t>Relatie met andere basismodellen</t>
-  </si>
-  <si>
-    <t>Ter Discussie</t>
-  </si>
-  <si>
-    <t>Data element</t>
-  </si>
-  <si>
-    <t>Uitleg</t>
-  </si>
-  <si>
-    <t>Uitkomst</t>
-  </si>
-  <si>
-    <t>ProbleemNaamSpecifiek</t>
-  </si>
-  <si>
-    <t>BgZ-MSZ 2.0</t>
-  </si>
-  <si>
-    <t>Dit is een gecodeerde naam, maar dit was ook om voor te sorteren op zib2020. In de mapping naar FHIR is zib2020 uiteindelijk gekozen om deze specificatie in een notitie te zetten, aangezien dat meer was wat gevraagd werd. Zie: https://nictiz.atlassian.net/browse/ZIBFHIR-145. Het voorstel is: Condition.code.text
-Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte,</t>
-  </si>
-  <si>
-    <t>Episodetitel</t>
-  </si>
-  <si>
-    <t>spoedsamenvatting 2.2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschrijving van het gezondheidsprobleem. Dit kan een door de zorgverlener geformuleerde tekst zijn, danwel de tekstuele omschrijving van de ICPC code. ter discussie: patient kan meerdere problemen onder 1 episode hebben -&gt; hoe dat in HIS gemodelleerd is, is onduidelijk. De ontvangende zorverlener is geinteresseerd in de episodelijst van de huisarts, omdat die een overzicht geeft van de conditions (problem-list) van de patient, waarbij condition.category=problemlist.item is. 
-https://referentiemodel.nhg.org/node/1594/publieksversie/published -&gt; diagnoses komen niet voor in het HIS, die zijn verdeeld onder episodes, of in de S-regel, of in de E-regel. de titel van de episode verandert in de loop van de tijd onder invloed van nieuwe inzichten of door het beloop van de aandoening, zoals de aanpassing van klacht naar diagnose (hoesten naar pneumonie), een nieuwe diagnose stelling (pneunomie wordt longcarcinoom) of de nuancering of verfijning van de diagnose (longcarcinoom naar longcarcinoom met metastases).  
-is episode een condition?
-</t>
-  </si>
-  <si>
-    <t>EHDS LIM</t>
-  </si>
-  <si>
-    <t>De vraag is of in de mapping naar FHIR hier nog naar een EHDS=professional gemapt kan worden, OF dat in LIM aangepast kan worden op iets wat FHIR aankan in de FHIR resource condition</t>
-  </si>
-  <si>
-    <t>Auteur.device</t>
-  </si>
-  <si>
-    <t>niet in FHIR wel in openEHR. komt hier een extension voor? Device wordt nu uitgewerkt in team carefuel</t>
-  </si>
-  <si>
-    <t>Indicates the patient or group who the condition record is associated with.</t>
-  </si>
-  <si>
-    <t>subject</t>
-  </si>
-  <si>
-    <t>Waarom zetten we groep er wel of niet bij? Nu niet meegenomen, maar wellicht voor in de toekomst?</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.4.3.11.60.153.4.30/2026-07-29T00:00:00</t>
-  </si>
-  <si>
-    <t>Identificatie van object gezondheidstoestand</t>
-  </si>
-  <si>
-    <t>De patiënt waarover de gezondheidstoestand gaat</t>
-  </si>
-  <si>
-    <t>Verwijziging naar Patient of Groep</t>
-  </si>
-  <si>
-    <t>De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. In bepaalde omstandigheden kan het echter ook om anderen gaan, bijvoorbeeld een orgaandonor, een foetus of een familielid.</t>
-  </si>
-  <si>
-    <t>Geeft aan aan welke patiënt of groep het dossier in kader van gezondheidstoestand is gekoppeld.</t>
-  </si>
-  <si>
-    <t>CON-1.4</t>
   </si>
   <si>
     <t>Nee, Kenmerken die relevant zijn voor een eenduidige definitie van het concept vormen de dataelementen van de zib. Een zib moet alle mogelijke eigenschappen van dat concept vatten voor zover relevant in gebruik van informatiesystemen binnen het zorg- en gezondheidsdomein
 Kenmerken die wel relevant zijn voor een compleet begrip, maar ook los van het concept herbruikbaar zijn worden als aparte zib middels een relaties vormgegeven</t>
   </si>
   <si>
+    <t>CON-1.1</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>De patiënt waarover de gezondheidstoestand gaat</t>
+  </si>
+  <si>
+    <t>Verwijzing naar Patient</t>
+  </si>
+  <si>
+    <t>1..1</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0</t>
+  </si>
+  <si>
+    <t>CON-1.2</t>
+  </si>
+  <si>
+    <t>Subject of care</t>
+  </si>
+  <si>
+    <t>De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. In bepaalde omstandigheden kan het echter ook om anderen gaan, bijvoorbeeld een orgaandonor, een foetus of een familielid.</t>
+  </si>
+  <si>
+    <t>Vewijzing naar Subject of Care</t>
+  </si>
+  <si>
+    <t>openEHR Problem/Diagnosis 1.7.4</t>
+  </si>
+  <si>
+    <t>CON-1.3</t>
+  </si>
+  <si>
+    <t>Geeft aan aan welke patiënt of groep het dossier in kader van gezondheidstoestand is gekoppeld.</t>
+  </si>
+  <si>
+    <t>Verwijziging naar Patient of Groep</t>
+  </si>
+  <si>
+    <t>CON-1.4</t>
+  </si>
+  <si>
+    <t>Onderwerp</t>
+  </si>
+  <si>
+    <t>NL-behoefte vanuit zib-2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
+NL-behoefte komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
+  </si>
+  <si>
+    <t>ZIB 2017  (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+Spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>CON-2</t>
+  </si>
+  <si>
+    <t>Identificatie van object gezondheidstoestand</t>
+  </si>
+  <si>
+    <t>Om het object uniek te identificeren in systemen</t>
+  </si>
+  <si>
+    <t>CON-2.1</t>
+  </si>
+  <si>
+    <t>header.identifier</t>
+  </si>
+  <si>
+    <t>Business identifier van het object</t>
+  </si>
+  <si>
+    <t>0..*</t>
+  </si>
+  <si>
+    <t>Ja (identifier)</t>
+  </si>
+  <si>
+    <t>Ja (architype.id) maar komt niet voor in de archetypen, maar komt naar voren bij het opslaan (originating_system_item_ids : DV_IDENTIFIER). is 0..*</t>
+  </si>
+  <si>
+    <t>Nee</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nee </t>
   </si>
   <si>
-    <t>CON-3.4</t>
-  </si>
-  <si>
-    <t>contactpersoon als auteur</t>
-  </si>
-  <si>
-    <t>auteur</t>
-  </si>
-  <si>
-    <t>nee</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EHDSCondition.header.author</t>
-  </si>
-  <si>
-    <t>LIMS omschrijving is "	
-The author of the condition information."  Het is gemapt met FHIR: Condition.recorder: de omschrijving is "Individual who recorded the record and takes responsibility for its content." -&gt; de registratie-persoon is niet altijd ook de verantwoordelijke.  Is dit een foute mapping?</t>
-  </si>
-  <si>
-    <t>Verwijzing naar patient, zorgverlener, contactpersoon</t>
-  </si>
-  <si>
-    <t>CON-6.1</t>
-  </si>
-  <si>
-    <t>Degene die de informatie heeft verschaft en instaat voor de juistheid ervan. Dit is niet altijd zorgverlener die de gegevens invoert in het informatiesysteem, maar het kan ook de patiënt zijn of een andere betrokkene zoals bv een ouder, mantelzorger of voogd.</t>
-  </si>
-  <si>
-    <t>Informatiebron</t>
-  </si>
-  <si>
-    <t>Het apparaat waar de informatie over de conditie vandaan komt</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ja (asserter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>ja, informatiebron als basiselement</t>
-  </si>
-  <si>
-    <t>nee, niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.</t>
-  </si>
-  <si>
-    <t>JA, auteur als basiselement</t>
-  </si>
-  <si>
-    <t>Auteur: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot bron van de informatie en de vastlegger in het dossier.</t>
-  </si>
-  <si>
-    <t>Zib 2017 https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf</t>
-  </si>
-  <si>
-    <t>Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf)</t>
-  </si>
-  <si>
-    <t>EHDS LIM EHDSCondition 1.0.0, Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
-Spoedsamenvatting 2.2.0</t>
-  </si>
-  <si>
-    <t>EHDS LIM EHDSCondition 1.0.0
-spoedsamenvatting 2.2.0</t>
+    <t>CON-2.2</t>
+  </si>
+  <si>
+    <t>Identificatie</t>
+  </si>
+  <si>
+    <t>Unieke identificatie van één specifieke episode. De unieke identificatie wordt gebruikt om één specifieke episode te herkennen binnen een lijst met alle episodes van een patiënt.</t>
+  </si>
+  <si>
+    <t>1..*</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>CON-3</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>De auteur van de informatie over de gezondheidstoestand.
+NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
+NL-behoefte komt te vervallen in zib2020</t>
+  </si>
+  <si>
+    <t>0..* Choice of types</t>
   </si>
   <si>
     <r>
@@ -1201,31 +559,89 @@
     </r>
   </si>
   <si>
-    <t>ZIB 2017  (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
-Spoedsamenvatting 2.2.0</t>
-  </si>
-  <si>
-    <t>NL-behoefte vanuit 2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
-NL-behoefte komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
-  </si>
-  <si>
-    <t>Om het object uniek te identificeren in systemen</t>
-  </si>
-  <si>
-    <t>De auteur van de informatie over de gezondheidstoestand.
-NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
-NL-behoefte komt te vervallen in zib2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De organisatie waaruit de informatie over de conditie afkomstig is.
-NL-behoefte: waarom/meerwaarde vanuit de spoedsamenvatting: om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; als in er kunnen verschillende zorgverleners werken bij dezelfde organisatie.-&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit  HL7standaard V3 CDA (custiodian en author) 
-Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder (bron: https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf ). </t>
+    <t>Ja (RM:other_participations)</t>
+  </si>
+  <si>
+    <t>Auteur: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot bron van de informatie en de vastlegger in het dossier.</t>
+  </si>
+  <si>
+    <t>JA, auteur als basiselement</t>
+  </si>
+  <si>
+    <t>CON-3.1</t>
+  </si>
+  <si>
+    <t>zorgverlener als auteur</t>
+  </si>
+  <si>
+    <t>authorEHDSHealthProfessional</t>
   </si>
   <si>
     <t xml:space="preserve">
 De zorgverlener die de informatie over de conditie invoert/registreert
 NL-behoefte: Waarom/meerwaarde vanuit de spoedsamenvatting; om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; Er kunnen verschillende zorgverleners werken bij dezelfde organisatie -&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit HL7standaard V3 CDA (custiodian en author) 
 </t>
+  </si>
+  <si>
+    <t>Verwijziging naar EHDSHealthProfessional</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0, Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+Spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>Ja (recorder = Practitioner of PractitionerRole)</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>CON-3.2</t>
+  </si>
+  <si>
+    <t>organisatie als auteur</t>
+  </si>
+  <si>
+    <t>authorEHDSOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De organisatie waaruit de informatie over de conditie afkomstig is.
+NL-behoefte: waarom/meerwaarde vanuit de spoedsamenvatting: om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; als in er kunnen verschillende zorgverleners werken bij dezelfde organisatie.-&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit  HL7standaard V3 CDA (custiodian en author) 
+Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder (bron: https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf ). </t>
+  </si>
+  <si>
+    <t>Verwijziging naar EHDSOrganization</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0
+spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>Ja (recorder.PracticionerRole.Organisation)</t>
+  </si>
+  <si>
+    <t>CON-3.3</t>
+  </si>
+  <si>
+    <t>apparaat als auteur</t>
+  </si>
+  <si>
+    <t>authorEHDSDevice</t>
+  </si>
+  <si>
+    <t>Het apparaat waar de informatie over de conditie vandaan komt</t>
+  </si>
+  <si>
+    <t>Verwijziging naar EHDSDevice</t>
+  </si>
+  <si>
+    <t>CON-3.4</t>
+  </si>
+  <si>
+    <t>contactpersoon als auteur</t>
+  </si>
+  <si>
+    <t>auteur</t>
   </si>
   <si>
     <r>
@@ -1259,24 +675,49 @@
     </r>
   </si>
   <si>
+    <t>Verwijzing naar patient, zorgverlener, contactpersoon</t>
+  </si>
+  <si>
+    <t>Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf)</t>
+  </si>
+  <si>
+    <t>nee</t>
+  </si>
+  <si>
+    <t>CON-4</t>
+  </si>
+  <si>
     <t>Datum en evt. tijd van registreren</t>
   </si>
   <si>
+    <t>CON-4.1</t>
+  </si>
+  <si>
+    <t>header.date</t>
+  </si>
+  <si>
     <t>Datum en eventueel tijdstip van opstellen/uitgeven</t>
   </si>
   <si>
-    <t>Bij een episode kan zowel de startdatum van de episode zelf (het begin van de contacten tussen arts en patiënt over een gezondheidskwestie) worden vastgelegd, als de begindatum van de in de episodetitel beschreven aandoening.
-Bij template kezo-Problemobservation  is De effectiveTime, ook biologisch relevante tijd genoemd, is het tijdstip waarop de waarneming geldt voor de patient. Voor een zorgverlener die een patiënt in de kliniek vandaag ziet en waar een voorgeschiedenis van een hartaanval wordt geconstatterd die vijf jaar geleden heeft plaatsgevonden, is de effectiveTime dus vijf jaar geleden.
-de reden voor IVL_TS is onbekend</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0 (https://decor.nictiz.nl/pub/acutezorg/acutezorg-html-20190117T230242/tmp-2.16.840.1.113883.2.4.3.11.60.66.10.213-2015-07-03T000000.html)</t>
+    <t>DatumTijd</t>
+  </si>
+  <si>
+    <t>0..1</t>
+  </si>
+  <si>
+    <t>Ja (recordedDate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja. Opmerking Wouter bij AllergieIntolerantie: metadata komt in elk archetype voor. </t>
+  </si>
+  <si>
+    <t>CON-4.2</t>
   </si>
   <si>
     <t xml:space="preserve">zorgepisode.startdatum </t>
   </si>
   <si>
-    <t>probleem.startdatum</t>
+    <t>HIS-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; cardinaliteit 1</t>
   </si>
   <si>
     <t>IVL_TS</t>
@@ -1285,30 +726,26 @@
     <t>Spoedsamenvatting 2.2.0 (bron: KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212)</t>
   </si>
   <si>
-    <t>NL-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; cardinaliteit 1</t>
-  </si>
-  <si>
-    <t>https://referentiemodel.nhg.org/
-https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf</t>
-  </si>
-  <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>Bron</t>
-  </si>
-  <si>
-    <t>Taal</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Condition model - EHDS Logical Information Models v1.0.0
-https://health.ec.europa.eu/publications/ehn-guideline-patient-summary_en</t>
-  </si>
-  <si>
-    <t>De status van de conditie. Requirement: eHN Guideline HDR (v1.1): A.2.6.1.7; PS (v3.4) A.2.2.2.1</t>
+    <t>CON-5</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status van het object </t>
+  </si>
+  <si>
+    <t>CON-5.1</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>De status beschrijft in welke staat het probleem zich bevindt:
+Actieve problemen zijn problemen waarbij de patiënt symptomen ervaart of waarvoor bewijs bestaat.
+Als de aandoening is afgenomen, moet de klinische status inactief, opgelost of in remissie zijn.
+Problemen met de status 'Inactief' verwijzen naar problemen die de patiënt niet langer beïnvloeden of waarvan het bestaan ​​niet langer is aangetoond.
+Requirement: eHN Guideline HDR (v1.1): A.2.6.1.7; PS (v3.4) A.2.2.2.1</t>
   </si>
   <si>
     <r>
@@ -1345,14 +782,817 @@
     </r>
   </si>
   <si>
-    <t>datumTijd</t>
+    <t>Ja (clinicalStatus)</t>
+  </si>
+  <si>
+    <t>Ja  0..1 (status) Problem/Diagnosis qualifier: Active/inactive met current/pass, mogelijk ook gecombineerd met level of control: Controlled Indeterminate Not controlled. En 'Remission status' Vraag aan Wouter: is dit allemaal te mappen op FHIR-uitwisseling?</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nictiz.atlassian.net/browse/PAT-301 </t>
+  </si>
+  <si>
+    <t>CON-5.2</t>
+  </si>
+  <si>
+    <t>HIS-behoefte: vanuit episode. De status is actief of open, danwel gesloten. bijbehorende problemen worden niet gesloten, maar episode wel. Indien een probleem evolueert, bijvoorbeeld van hoesten naar longontsteking, dan verandert de episodenaam.
+Zib 2017: De probleemstatus beschrijft de toestand van het probleem: Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
+Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
+  </si>
+  <si>
+    <t>spoedsamenvatting: open, gesloten, gesloten met attentiewaarde (= active/remission/resolved; episodes uit het verleden die niet meer actueel zijn, maar die de huisarts toch in beeld wil houden., bijvoorbeeld hartinfact in verleden.)
+ZIB 2017-ZIB2020: actueel, niet actueel
+ZIB2024: aandoeningOfGesteldheid:Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0; Zib 2017; zib 2020</t>
+  </si>
+  <si>
+    <t>CON-6</t>
+  </si>
+  <si>
+    <t>Bron</t>
+  </si>
+  <si>
+    <t>CON-6.1</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf of zijn/haar naaste. Gebruikt in gevallen waarin de patiënt de informatie zelf heeft opgesteld of de auteur door de patiënt verstrekte informatie heeft aangeleverd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gecodeerde concept </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ja (asserter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PAT-306</t>
+    </r>
+  </si>
+  <si>
+    <t>Ja (Reference model: Information Provider) 0..1 Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software.</t>
+  </si>
+  <si>
+    <t>nee, niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.</t>
+  </si>
+  <si>
+    <t>ja, informatiebron als basiselement</t>
+  </si>
+  <si>
+    <t>ja met zib registratiegegevens</t>
+  </si>
+  <si>
+    <t>[PAT-306] header.source mapping FHIR condition.asserter - BITS - Jira</t>
+  </si>
+  <si>
+    <t>CON-6.2</t>
+  </si>
+  <si>
+    <t>Information Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Een persoon of instantie die de informatie heeft verstrekt. Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software. Het wordt over het algemeen alleen gebruikt wanneer de informatieverstrekker expliciet moet worden vermeld 
+</t>
+  </si>
+  <si>
+    <t>party proxy. referentie na een ID van een:
+* the patient
+* a patient agent, e.g. parent, guardian
+* the clinician
+* a device or software</t>
+  </si>
+  <si>
+    <t>CON-6.3</t>
+  </si>
+  <si>
+    <t>Informatiebron</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>NL-behoefte zib 2017: Degene die de informatie heeft verschaft en instaat voor de juistheid ervan. Dit is niet altijd zorgverlener die de gegevens invoert in het informatiesysteem, maar het kan ook de patiënt zijn of een andere betrokkene zoals bv een ouder, mantelzorger of voogd.
+NL-behoefte in zib2020 komt te vervallen: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.
+NL-behoefte zib2024: Indien de vastgelegde informatie niet door de behandelend arts zelf is vastgesteld, kan de bron van de informatie vastgelegd worden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">. of wijzevanverkrijgen?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Geen behoefte vanuit spoedsamenvatting om de bron vast te leggen; bron van de informatie zoals beschreven in de LIM is mogelijk wat anders dan bronsysteem 'wie is eigenaar van de vastgestelde aandoening'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">zib2017:patient, contactpersoon, zorgverlener
+zib2020:geen
+zib2024:patient, zorgverlener, contactpersoon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">of vrije tekst
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>spoedsamenvatting: geen</t>
+    </r>
+  </si>
+  <si>
+    <t>Zib 2017 https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf
+ZIB2020
+ZIB2024 https://www.zibs.nl/wiki/RegistratieGegevens-v1.1.2(2024NL)
+spoedsamenvatting</t>
+  </si>
+  <si>
+    <t>CON-7</t>
+  </si>
+  <si>
+    <t>Taal</t>
+  </si>
+  <si>
+    <t>De taal waarin het object is geschreven.De taal wordt aangegeven met de IETF-taalcode.</t>
+  </si>
+  <si>
+    <t>Waardelijst BCP 47</t>
+  </si>
+  <si>
+    <t>Ja (language)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ja
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Opmerking Wouter bij AllergieIntolerantie: metadata komt in elk archetype voor. </t>
+    </r>
+  </si>
+  <si>
+    <t>CON-8</t>
+  </si>
+  <si>
+    <t>Naam van de conditie</t>
+  </si>
+  <si>
+    <t>Ja (code, 0..1)</t>
+  </si>
+  <si>
+    <t>Ja (Problem / Diagnosis name)</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemNaam</t>
+  </si>
+  <si>
+    <t>CON-8.1</t>
+  </si>
+  <si>
+    <t>problem</t>
+  </si>
+  <si>
+    <t>Code die de aandoening, het probleem of de diagnose identificeert</t>
+  </si>
+  <si>
+    <t>Waardelijst (preferred): ICD-10, SNOMED CT, ICD-O, Orphacode if rare disease is diagnosed</t>
+  </si>
+  <si>
+    <t>CON-8.2</t>
+  </si>
+  <si>
+    <t>Problem/Diagnosis name</t>
+  </si>
+  <si>
+    <t>Identificatie van het probleem of de diagnose, met de naam erbij.
+Opmerking: Codering van de naam van het probleem of de diagnose met een terminologie heeft de voorkeur, indien mogelijk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String of waardelijst </t>
+  </si>
+  <si>
+    <t>CON-8.3</t>
+  </si>
+  <si>
+    <t>ProbleemNaam</t>
+  </si>
+  <si>
+    <t>De probleemnaam definieert het probleem. Afhankelijk van de setting kunnen verschillende codestelsels worden gebruikt. De ProbleemNaamCodelijst geeft een overzicht van de mogelijke codestelsels</t>
+  </si>
+  <si>
+    <t>Waardelijst (DHD Diagnosethesaurus; ICD-10, dutch translation; SNOMED CT; NANDA-I; ICF; ICPC-1 NL; DSM-IV; DSM-5; GGZ Diagnoselijst)</t>
+  </si>
+  <si>
+    <t>Zib 2017, zib 2020</t>
+  </si>
+  <si>
+    <t>CON-8.4</t>
+  </si>
+  <si>
+    <t>zorgepisodetitel</t>
+  </si>
+  <si>
+    <t>Beschrijving van het gezondheidsprobleem. Dit kan een door de zorgverlener geformuleerde tekst zijn, danwel de tekstuele omschrijving van de ICPC code. In het HIS-referentiemodel is de "episode-label" bij een episode-item beschreven. Dat geeft de episode-titel weer op het moment van vastleggen van het episode-item. Door na te gaan wat de episodelabels waren van de episode-items(=Een gegeven van de patiënt dat mede de toestand van een patiënt op een bepaald moment beschrijft in het kader van een episode), die tot de episode horen, zijn dus de aanpassingen te achterhalen. Dit zit al jaren zo in het HIS-Referentiemodel. De vraag is of HIS’en dit ook op deze manier hebben geïmplementeerd. de episode blijft dezelfde episode bij een aanpassing van de naam; Het haakje / unieke ID van de episode verandert niet. 
+Een gezondheidskwestie kan zich in de loop der tijd ontwikkelen. Bijvoorbeeld een patiënt met eenvoudige verkoudheid wordt steeds zieker als die verkoudheid zich verder ontwikkelt tot een pneumonie. De huisarts zal de gezondheidskwestie hier aanvankelijk een verkoudheid noemen, maar de klachten later omschrijven als een pneumonie. Hij past de aard (de titel) van de episode in de loop van de tijd aan van verkoudheid naar pneumonie.</t>
+  </si>
+  <si>
+    <t>Waardelijst (ICPC) + tekstuele omschrijving</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0 https://referentiemodel.nhg.org/node/1487/volledig/published</t>
+  </si>
+  <si>
+    <t>CON-9</t>
+  </si>
+  <si>
+    <t>Begin datum van de conditie</t>
+  </si>
+  <si>
+    <t>De datum en evt. tijd waarop de gezondheidstoestand  is begonnen</t>
+  </si>
+  <si>
+    <t>niet toekomst</t>
+  </si>
+  <si>
+    <t>Ja (onsetDateTime)</t>
+  </si>
+  <si>
+    <t>ja 0..1 Date/time of onset</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemBeginDatum</t>
+  </si>
+  <si>
+    <t>CON-9.1</t>
+  </si>
+  <si>
+    <t>onsetDate</t>
+  </si>
+  <si>
+    <t>De datum waarop de conditie/probleem is begonnen</t>
+  </si>
+  <si>
+    <t>CON-9.2</t>
+  </si>
+  <si>
+    <t>ProbleemBeginDatum</t>
+  </si>
+  <si>
+    <t>Begin van de aandoening, waarop het probleem betrekking heeft. Vooral bij klachten waarbij het langer duurt voordat de uiteindelijke diagnose gesteld wordt is het belangrijk niet alleen de diagnosedatum te weten, maar ook sinds wanneer de aandoening al bestaat. Een vage datum, bijv. alleen een jaartal of een maand en een jaartal, is toegestaan.
+NL-behoefte: ZIB2020 Definitie van concept ProbleemBeginDatum is aangepast om duidelijker te maken dat bij type diagnose het gaat om de datum waarop de diagnose gesteld is en niet om de begindatum van het probleem
+NL behoefte zib2024: Uit de analyse van de door de NHG ingebrachte wijzigingsvoorstellen is naar voren gekomen dat er behoefte is om een onderscheid te maken tussen begin-/eind- datum van de diagnose (probleem) en begin-/eind- datum van onderliggend lijden</t>
+  </si>
+  <si>
+    <t>Date, Time, DateTime</t>
+  </si>
+  <si>
+    <t>Zib 2017; zib 2020</t>
+  </si>
+  <si>
+    <t>CON-9.3</t>
+  </si>
+  <si>
+    <t>episode.begindatum aandoening</t>
+  </si>
+  <si>
+    <t>Bij een episode kan zowel de startdatum van de episode zelf (het begin van de contacten tussen arts en patiënt over een gezondheidskwestie) worden vastgelegd, als de begindatum van de in de episodetitel beschreven aandoening.
+Bij template kezo-Problemobservation  is De effectiveTime, ook biologisch relevante tijd genoemd, is het tijdstip waarop de waarneming geldt voor de patient. Voor een zorgverlener die een patiënt in de kliniek vandaag ziet en waar een voorgeschiedenis van een hartaanval wordt geconstatterd die vijf jaar geleden heeft plaatsgevonden, is de effectiveTime dus vijf jaar geleden.</t>
+  </si>
+  <si>
+    <t>begindatum aandoening:Datumtijd [0..1]
+spoedsamenvatting in artdecor geeft aan: IVL_TS (behoefte van deze datatype is onbekend)</t>
+  </si>
+  <si>
+    <t>HIS-referentiemodel: https://referentiemodel.nhg.org/node/93/volledig/published
+Spoedsamenvatting 2.2.0 (https://decor.nictiz.nl/pub/acutezorg/acutezorg-html-20190117T230242/tmp-2.16.840.1.113883.2.4.3.11.60.66.10.213-2015-07-03T000000.html)</t>
+  </si>
+  <si>
+    <t>CON-10</t>
+  </si>
+  <si>
+    <t>Eind datum van de gezondheidstoestand</t>
+  </si>
+  <si>
+    <t>De datum en evt. tijd waarop de gezondheidstoestand is afgelopen</t>
+  </si>
+  <si>
+    <t>verleden</t>
+  </si>
+  <si>
+    <t>Ja (abatementDateTime)</t>
+  </si>
+  <si>
+    <t>ja 0..1 Date/time of resolution</t>
+  </si>
+  <si>
+    <t>CON-10.1</t>
+  </si>
+  <si>
+    <t>endDate</t>
+  </si>
+  <si>
+    <t>De datum of geschatte datum waarop de conditie in remissie ging of verdween</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemEindDatum</t>
+  </si>
+  <si>
+    <t>CON-10.2</t>
+  </si>
+  <si>
+    <t>ProbleemEindDatum</t>
+  </si>
+  <si>
+    <t>Datum waarop de aandoening, waarop het probleem betrekking heeft, als niet meer aanwezig wordt beschouwd. Deze datum hoeft niet gelijk te zijn aan de datum waarop de statuswijzinging van het probleem is vastgelegd. Een vage datum, bijv. alleen een jaartal of een maand en een jaartal, is toegestaan.</t>
+  </si>
+  <si>
+    <t>TS (maar vage datum mag ook)</t>
+  </si>
+  <si>
+    <t>CON-10.3</t>
+  </si>
+  <si>
+    <t>zorgepisode.Einddatum</t>
+  </si>
+  <si>
+    <t>HIS-behoefte:
+Voor het afsluiten van een episode zijn verschillende behoefte:
+De huisarts sluit de episode handmatig af.
+De huisarts legt bij de episode een verwachte einddatum vast. Bij voortschrijdend inzicht over de verwachte duur van de episode past de huisarts de verwachte einddatum aan. De episode sluit automatisch na het verstrijken van de vastgelegde einddatum.
+In de praktijk wordt de keuze gemaakt om te werken met een vast termijn waarna een episode wordt afgesloten. De termijn gaat in vanaf het moment waarop de episode het laatst is gewijzigd. Een wijziging kan zijn een aanpassing van de titel of het toevoegen van gegevens (bijvoorbeeld een SOEP-verslag). Om welke termijn het gaat wordt vastgesteld op praktijkniveau. De episode sluit automatisch na het verstrijken van het termijn.
+Indien een episodenaam wijzigt doordat er een andere ICPC-code en naam (handmatig of door episode-item), vanwege dat de aandoening verandert van hoesten naar longontsteking krijgt de oude versie geen einddatum. Huisartsen leggen niet het concept probleem vast, dus er is geen zib-probleemeinddatum)</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0 (https://referentiemodel.nhg.org/node/93/volledig/published)</t>
+  </si>
+  <si>
+    <t>CON-11</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Categorie(ën) van het probleem (bijv. POA - aanwezig bij opname, HAC - in het ziekenhuis opgelopen aandoening, en andere categorisaties. Door de probleemcategorie te kiezen, kunnen aandoeningen die tijdens het ziekenhuisverblijf zijn ontstaan, worden gemarkeerd. Het is een behoefte uit de discharge report. https://health.ec.europa.eu/system/files/2024-01/ehn_hdr_guidelines_en.pdf</t>
+  </si>
+  <si>
+    <t>Ja (category)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disorder category via Problem/Diagnosis qualifier. Vraag aan Wouter/Michal: hoe werkt dat in openEHR, want in welk data-element wordt dit cluster in een slot gestopt,status? de keuze inopenEHR is tussen 'principle, secondary en complication'... dat is niet helemaal wat de LIM wil aangeven: die heeft als voorbeeld "present on admission, HAC - hospital aquired condition, and other categorisations" en in FHIR hebben ze weer andere voorbeelden problem-list-item | encounter-diagnosis </t>
+  </si>
+  <si>
+    <t>CON-11.1</t>
+  </si>
+  <si>
+    <t>Bij opvragen van de spoedsamenvatting vanuit de huisarts wordt de episodelijst opgevraagd van relevante aandoeningen. dit vertaalt naar de HIS door open episodes en gesloten episode met attentiewaarde</t>
+  </si>
+  <si>
+    <t>Gecodeerde concept : problem-list-item</t>
+  </si>
+  <si>
+    <t>spoedsamenvatting 2.2.0</t>
+  </si>
+  <si>
+    <t>CON-11.2</t>
+  </si>
+  <si>
+    <t>ZIB2024: isComplicatie is een element van diagnostischInzicht; Geeft aan of het diagnostisch inzicht wel of niet een complicatie betreft. Relevante achtergrondinformatie staat in de https://demedischspecialist.nl/sites/default/files/2022-07/handreiking_adequate_registratie_in_het_epd.pdf die vorig jaar is opgesteld."Het registreren van complicaties is ook onderdeel van de zib probleem. Complicatieregistratie is een relevante registratie die gebruikt wordt voor
+in-en externe kwaliteitscontroles en ter verbetering van zorg. "</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>ZIB2024</t>
+  </si>
+  <si>
+    <t>Ja disorder category</t>
+  </si>
+  <si>
+    <t>CON-12</t>
+  </si>
+  <si>
+    <t>resolutionCircumstances</t>
+  </si>
+  <si>
+    <t>Beschrijft de reden waarom de status van het probleem is veranderd van actueel naar inactief (bijv. chirurgische ingreep, medische behandeling, enz.).</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Ja? (note.text)</t>
+  </si>
+  <si>
+    <t>Ja? Comment</t>
+  </si>
+  <si>
+    <t>geen NL behoefte van ZIB of spoedsamenvatting voor dit element gevonden om dit gestructureerd te registeren. Huisartsen leggen dit vast in de episodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
+  </si>
+  <si>
+    <t>CON-13</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>Een subjectieve beoordeling van de ernst van de aandoening, zoals vastgesteld door de arts.</t>
+  </si>
+  <si>
+    <t>Waardelijst (preferred): HL7 Condition/Diagnosis Severity; SNOMED CT</t>
+  </si>
+  <si>
+    <t>heden</t>
+  </si>
+  <si>
+    <t>Ja  (Severity)</t>
+  </si>
+  <si>
+    <t>Ja Severity (optional)</t>
+  </si>
+  <si>
+    <t>CON-13.1</t>
+  </si>
+  <si>
+    <t>geen NL behoefte van ZIB2017 en ZIB2020 of spoedsamenvatting voor dit element gevonden om gestructureerd te registeren: Huisartsen registreren de ernst in de episodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
+  </si>
+  <si>
+    <t>CON-13.2</t>
+  </si>
+  <si>
+    <t>Ernst</t>
+  </si>
+  <si>
+    <t>NL behoefte zib2024: element ernst in zib aandoeningofgesteldheid. Duiding van de ernst van de aandoening of gesteldheid. Een aandoening of gesteldheid kan weinig klachten geven en toch ernstig zijn, maar het omgekeerde kan ook. -&gt; Wie deze wens heeft en waarom is niet gevonden in ZIB-project.</t>
+  </si>
+  <si>
+    <t>Waardelijst: Licht, Licht tot matig, Matig, Matig tot ernstig, Ernstig, Van levensbedreigende ernst, Levensbedreigend, Fataal</t>
+  </si>
+  <si>
+    <t>CON-14</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t>De anatomische locatie, inclusief de zijde waar deze aandoening zich manifesteert.</t>
+  </si>
+  <si>
+    <t>Verwijziging naar EHDSBodyStructure</t>
+  </si>
+  <si>
+    <t>Ja (bodySite)</t>
+  </si>
+  <si>
+    <t>Ja (StructuredBodySite)</t>
+  </si>
+  <si>
+    <t>CON-14.1</t>
+  </si>
+  <si>
+    <t>ProbleemAnatomischeLocatie</t>
+  </si>
+  <si>
+    <t>Anatomische locatie die de focus is van de verrichting.</t>
+  </si>
+  <si>
+    <t>CON-14.2</t>
+  </si>
+  <si>
+    <t>ProbleemLateraliteit</t>
+  </si>
+  <si>
+    <t>Lateraliteit verbijzondert de anatomische locatie door, indien van toepassing, de zijdigheid vast te leggen, bijvoorbeeld links.</t>
+  </si>
+  <si>
+    <t>CON-15</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>Het stadium/de graad wordt doorgaans formeel beoordeeld aan de hand van een specifiek stadium-/gradatiesysteem. Er kunnen meerdere beoordelingssystemen worden gebruikt.</t>
+  </si>
+  <si>
+    <t>Waardelijst (preferred): e.g. TNM, ICD-O-3, Bi-Rads, Li-Rads, …</t>
+  </si>
+  <si>
+    <t>Ja (stage)</t>
+  </si>
+  <si>
+    <t>Ja/Nee maar via extensie / uitbreiding van archetype Specific Details (cluster?) -&gt; Wouter vragen.</t>
+  </si>
+  <si>
+    <t>https://nictiz.atlassian.net/browse/PAT-304</t>
+  </si>
+  <si>
+    <t>HIS-behoefte: classificaties , zoals TNM, worden geregistreerd in de eipsodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
+  </si>
+  <si>
+    <t>CON-16</t>
+  </si>
+  <si>
+    <t>Status van verificatie van de conditie</t>
+  </si>
+  <si>
+    <t>CON-16.1</t>
+  </si>
+  <si>
+    <t>diagnosisAssertionStatus</t>
+  </si>
+  <si>
+    <t>Een bewering over de zekerheid die aan een diagnose is verbonden. Diagnostisch en/of klinisch bewijs van een aandoening</t>
+  </si>
+  <si>
+    <t>Waardelijst (preferred): HL7 Condition Verification Status (unconfirmed, provisional, differential, confirmed, refuted, entered-in-error )</t>
+  </si>
+  <si>
+    <t>Ja (verificationStatus)</t>
+  </si>
+  <si>
+    <t>Ja? DiagnosticCertainty? proberbly, confermed, supsected OF VIA cluster "Diagnostic status" : Preliminary ; Working ; Established ; Refuted</t>
+  </si>
+  <si>
+    <t>VerificatieStatus ZIB!</t>
+  </si>
+  <si>
+    <t>CON-P16.2</t>
+  </si>
+  <si>
+    <t>VerificatieStatus</t>
+  </si>
+  <si>
+    <t>Klinische status van het probleem of de diagnose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VerificatieStatusCodelijst </t>
+  </si>
+  <si>
+    <t>CON-17</t>
+  </si>
+  <si>
+    <t>specialistContact</t>
+  </si>
+  <si>
+    <t>Een zorgverlener die specifiek betrokken is bij het probleem, als voorkeurscontactpersoon.</t>
+  </si>
+  <si>
+    <t>Verwijzing naar de EHDSHealthProfessional</t>
+  </si>
+  <si>
+    <t>Ja note.text/careteam.reason</t>
+  </si>
+  <si>
+    <t>Onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is -&gt; Wouter vragen</t>
+  </si>
+  <si>
+    <t>CON-18</t>
+  </si>
+  <si>
+    <t>externalResource</t>
+  </si>
+  <si>
+    <t>Externe bronnen die specifiek betrekking hebben op het probleem, bijvoorbeeld een link naar een probleem met een zeldzame ziekte en de bijbehorende richtlijnen</t>
+  </si>
+  <si>
+    <t>uri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0..* </t>
+  </si>
+  <si>
+    <t>Ja(structureDefinition.extension:relatedArtifact) FMM2</t>
+  </si>
+  <si>
+    <t>ja/nee Guideline Identifier (focust op richtlijnen of breder, LIM is breder)</t>
+  </si>
+  <si>
+    <t>CON-19</t>
+  </si>
+  <si>
+    <t>Toelichting van diegene die het Probleem heeft vastgesteld of bijgewerkt.</t>
+  </si>
+  <si>
+    <t>Ja (note)</t>
+  </si>
+  <si>
+    <t>Ja (comment)</t>
+  </si>
+  <si>
+    <t>CON-20</t>
+  </si>
+  <si>
+    <t>NadereSpecificatieProbleemNaam</t>
+  </si>
+  <si>
+    <t>BGZ-MSZ- behoefte: Wat is precies de behoefte van MBZ-MSZ voor een waardelijst als een naderespecificatie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String en waardelijst </t>
+  </si>
+  <si>
+    <t>Zib 2020; informatiestandaard BgZ-MSZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja/nee (code.text) </t>
+  </si>
+  <si>
+    <t>Ja, variant (tekst or coded tekst)</t>
+  </si>
+  <si>
+    <t>Actie</t>
+  </si>
+  <si>
+    <t>Notitie</t>
+  </si>
+  <si>
+    <t>[Actie om te ondernemen, kies uit de 3 acties: cluster, andere bouwsteen en modelleren]</t>
+  </si>
+  <si>
+    <t>[Eventuele notitie]</t>
+  </si>
+  <si>
+    <t>[Naam van de informatie-requirement ]</t>
+  </si>
+  <si>
+    <t>In het FHIR profiel is er voor de referentie voor auteur.Device nog geen Device profiel toegevoegd omdat nlcore-device nog niet bestaat. Deze moet tzt wel toegevoegd worden.</t>
+  </si>
+  <si>
+    <t>Potentiële basismodellen</t>
+  </si>
+  <si>
+    <t>FHIR R4 resource Condition
+openEHR archetype Problem/Diagnosis 1.7.3</t>
+  </si>
+  <si>
+    <t>Relatie met andere basismodellen</t>
+  </si>
+  <si>
+    <t>Ter Discussie</t>
+  </si>
+  <si>
+    <t>Data element</t>
+  </si>
+  <si>
+    <t>Uitleg</t>
+  </si>
+  <si>
+    <t>Uitkomst</t>
+  </si>
+  <si>
+    <t>ProbleemNaamSpecifiek</t>
+  </si>
+  <si>
+    <t>BgZ-MSZ 2.0</t>
+  </si>
+  <si>
+    <t>Dit is een gecodeerde naam, maar dit was ook om voor te sorteren op zib2020. In de mapping naar FHIR is zib2020 uiteindelijk gekozen om deze specificatie in een notitie te zetten, aangezien dat meer was wat gevraagd werd. Zie: https://nictiz.atlassian.net/browse/ZIBFHIR-145. Het voorstel is: Condition.code.text
+Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte,</t>
+  </si>
+  <si>
+    <t>Episodetitel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschrijving van het gezondheidsprobleem. Dit kan een door de zorgverlener geformuleerde tekst zijn, danwel de tekstuele omschrijving van de ICPC code. ter discussie: patient kan meerdere problemen onder 1 episode hebben -&gt; hoe dat in HIS gemodelleerd is, is onduidelijk. De ontvangende zorverlener is geinteresseerd in de episodelijst van de huisarts, omdat die een overzicht geeft van de conditions (problem-list) van de patient, waarbij condition.category=problemlist.item is. 
+https://referentiemodel.nhg.org/node/1594/publieksversie/published -&gt; diagnoses komen niet voor in het HIS, die zijn verdeeld onder episodes, of in de S-regel, of in de E-regel. de titel van de episode verandert in de loop van de tijd onder invloed van nieuwe inzichten of door het beloop van de aandoening, zoals de aanpassing van klacht naar diagnose (hoesten naar pneumonie), een nieuwe diagnose stelling (pneunomie wordt longcarcinoom) of de nuancering of verfijning van de diagnose (longcarcinoom naar longcarcinoom met metastases).  
+is episode een condition?
+</t>
+  </si>
+  <si>
+    <t>EHDS LIM</t>
+  </si>
+  <si>
+    <t>De vraag is of in de mapping naar FHIR hier nog naar een EHDS=professional gemapt kan worden, OF dat in LIM aangepast kan worden op iets wat FHIR aankan in de FHIR resource condition</t>
+  </si>
+  <si>
+    <t>Auteur.device</t>
+  </si>
+  <si>
+    <t>niet in FHIR wel in openEHR. komt hier een extension voor? Device wordt nu uitgewerkt in team carefuel</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>Indicates the patient or group who the condition record is associated with.</t>
+  </si>
+  <si>
+    <t>Waarom zetten we groep er wel of niet bij? Nu niet meegenomen, maar wellicht voor in de toekomst?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EHDSCondition.header.author</t>
+  </si>
+  <si>
+    <t>LIMS omschrijving is "	
+The author of the condition information."  Het is gemapt met FHIR: Condition.recorder: de omschrijving is "Individual who recorded the record and takes responsibility for its content." -&gt; de registratie-persoon is niet altijd ook de verantwoordelijke.  Is dit een foute mapping?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FHIR Condition Maturity Level: 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> openEHR Problem/Diagnosis;latest revision / latest published  53 [1.7.4] 
+Na analyse blijkt FHIR beste keus, want: 
+-categorie: bij openEHR zijn de keuzes voor cathegorie niet overeenkomend met de cathegorieen van de LIM -&gt; maar hoeft niet persé een deal-breaker te zijn
+- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR(mist differential en netered-in-error), wel volledige mapping met FHIR
+- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
+- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
+-specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1375,6 +1615,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1490,30 +1737,10 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1585,21 +1812,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1610,26 +1840,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1638,76 +1869,61 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -1886,6 +2102,25 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment wrapText="1"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2017,7 +2252,7 @@
       <xdr:rowOff>223837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>2181225</xdr:rowOff>
@@ -2027,7 +2262,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECAA1215-2A99-4248-92C1-D8603DD25A54}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7E9BA32-9F57-9DBE-09F8-19BB04854D12}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2036,7 +2271,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="161925" y="223837"/>
-          <a:ext cx="6802755" cy="1957388"/>
+          <a:ext cx="6705600" cy="1957388"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2593,40 +2828,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Uitleg"/>
-      <sheetName val="Concept"/>
-      <sheetName val="Bronnen informatiebehoefte"/>
-      <sheetName val="Niet geconsolideerde info"/>
-      <sheetName val="Informatiebehoefte"/>
-      <sheetName val="Ongedekte informatiebehoefte"/>
-      <sheetName val="Overwegingen voor de toekomst"/>
-      <sheetName val="zib-centrum JIRA"/>
-      <sheetName val="Basismodel "/>
-      <sheetName val="Template informatiebehoefte - A"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Chevy Susanto" id="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" userId="S::chevy.susanto@nictiz.nl::4e93d0cc-e599-42c6-82b7-6ffb715c7e27" providerId="AD"/>
@@ -2636,6 +2837,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}" name="Tabel2" displayName="Tabel2" ref="A2:C13" totalsRowShown="0">
+  <autoFilter ref="A2:C13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
@@ -2649,9 +2862,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N52" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:N52" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N60" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:N60" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
@@ -2672,7 +2885,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D40E6C54-E02A-43EF-B5CE-2ED10C0E81CC}" name="Tabel4" displayName="Tabel4" ref="A1:B10" totalsRowShown="0">
   <autoFilter ref="A1:B10" xr:uid="{D40E6C54-E02A-43EF-B5CE-2ED10C0E81CC}"/>
   <tableColumns count="2">
@@ -2683,7 +2896,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}" name="Tabel36" displayName="Tabel36" ref="B3:E9" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B3:E9" xr:uid="{87319CEB-0666-49DA-BC74-CF83CFEF5B56}"/>
   <tableColumns count="4">
@@ -3013,31 +3226,35 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J20" dT="2026-07-16T05:50:21.33" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{903FD87C-9891-4AE1-9361-7224FCD06B01}">
-    <text> active
- inactive
- resolved
- in remission
- evolution status - initial, interim/working, final; temporal status - current, past; episodicity status - first, new, ongoing; admission status - admission, discharge; or priority status - primary, secondary.</text>
+  <threadedComment ref="C5" dT="2026-08-17T11:32:29.22" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{CD16CA43-E215-4DCF-A4C0-2D380EB1C0BC}">
+    <text xml:space="preserve">Uit Scope en Usage van Condition FHIR R4 v4.0.1 </text>
   </threadedComment>
-  <threadedComment ref="K20" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
+    <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
+  </threadedComment>
+  <threadedComment ref="K21" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
     <text>1. Actief
 2. Inactief
 Kortere waardelijst</text>
   </threadedComment>
-  <threadedComment ref="K25" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+  <threadedComment ref="K27" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
     <text>Wel in metadata!</text>
   </threadedComment>
-  <threadedComment ref="E28" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+  <threadedComment ref="E30" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
   </threadedComment>
-  <threadedComment ref="B30" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+  <threadedComment ref="B32" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C30" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+  <threadedComment ref="C32" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C38" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C40" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
   </threadedComment>
 </ThreadedComments>
@@ -3046,15 +3263,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="218.44140625" customWidth="1"/>
+    <col min="1" max="1" width="218.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3063,7 +3280,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3079,384 +3296,367 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E1B5B8-C013-4DD1-9595-10AFF6D9F062}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="190.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="190.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="219.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
-    </row>
-    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="39"/>
-    </row>
-    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="408" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-    </row>
-    <row r="6" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-    </row>
-    <row r="7" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="40"/>
-    </row>
-    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="41"/>
-    </row>
-    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="40"/>
-    </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="39"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="43"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="43"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="42"/>
-      <c r="C18" s="38"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="38"/>
-      <c r="C21" s="43"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="42"/>
-      <c r="C24" s="38"/>
+        <v>27</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="349.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="7"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C10" r:id="rId1" display="https://www.hl7.org/fhir/R4/condition.html" xr:uid="{6169B330-2124-4ACC-9C33-24AFE1D4848F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="51.33203125" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="51.28515625" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3482,147 +3682,143 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:O58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="87.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" customWidth="1"/>
-    <col min="8" max="8" width="32.44140625" customWidth="1"/>
-    <col min="9" max="9" width="28.109375" customWidth="1"/>
-    <col min="10" max="10" width="51.33203125" customWidth="1"/>
-    <col min="11" max="11" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="38.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="78" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="32.42578125" customWidth="1"/>
+    <col min="9" max="9" width="28.140625" customWidth="1"/>
+    <col min="10" max="10" width="51.28515625" customWidth="1"/>
+    <col min="11" max="11" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="38.5703125" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>58</v>
+        <v>70</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="8"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>78</v>
       </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="9"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="D5" s="3" t="s">
-        <v>299</v>
+        <v>91</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3631,26 +3827,26 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7" t="s">
-        <v>73</v>
+    <row r="6" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3659,26 +3855,26 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
-        <v>274</v>
+    <row r="7" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>326</v>
+        <v>101</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>325</v>
+        <v>42</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3687,20 +3883,27 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8" s="7"/>
+    <row r="8" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3708,332 +3911,332 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
-      </c>
+    <row r="9" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="8"/>
       <c r="D9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>88</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>303</v>
-      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="3"/>
+    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>110</v>
+      </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="L10" s="3" t="s">
-        <v>303</v>
+        <v>117</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="9"/>
+    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>328</v>
+        <v>120</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>319</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>318</v>
+        <v>117</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>99</v>
-      </c>
+    <row r="12" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>322</v>
+        <v>94</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>303</v>
+        <v>130</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>103</v>
+    <row r="13" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>323</v>
+        <v>136</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>303</v>
+        <v>117</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>108</v>
+    <row r="14" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>304</v>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>146</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>331</v>
+        <v>148</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>310</v>
+        <v>150</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>307</v>
+        <v>138</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" s="3"/>
+    <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>116</v>
-      </c>
+    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>119</v>
+    <row r="18" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>160</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>340</v>
+        <v>162</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="3"/>
+    <row r="19" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="D19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -4041,299 +4244,309 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>124</v>
-      </c>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>348</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>131</v>
+    <row r="21" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>175</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>349</v>
+        <v>177</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>178</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="F22" s="3"/>
+      <c r="N21" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="22"/>
+      <c r="H22" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="35"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>116</v>
-      </c>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="L23" s="35" t="s">
-        <v>316</v>
-      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="37"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>311</v>
+    <row r="24" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="35" t="s">
-        <v>313</v>
+      <c r="C24" s="24" t="s">
+        <v>190</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="C25" s="9"/>
+        <v>94</v>
+      </c>
+      <c r="I24" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="L24" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="24" t="s">
+        <v>200</v>
+      </c>
       <c r="D25" s="3" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L25" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="I25" s="39"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="40"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="F26" s="3"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>145</v>
-      </c>
+      <c r="H26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>147</v>
-      </c>
+    <row r="27" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" s="10"/>
       <c r="D27" s="3" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>75</v>
-      </c>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>154</v>
+    <row r="29" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>219</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
-        <v>159</v>
+    <row r="30" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>223</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>162</v>
+        <v>226</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -4342,651 +4555,856 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="9"/>
+    <row r="31" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="D31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>170</v>
+    <row r="32" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>76</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3" t="s">
-        <v>174</v>
-      </c>
+    <row r="33" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" s="10"/>
       <c r="D33" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="3"/>
+        <v>239</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>177</v>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
+        <v>94</v>
+      </c>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="9"/>
+    <row r="35" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="D35" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>183</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="32"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>184</v>
+    <row r="36" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3" t="s">
-        <v>189</v>
-      </c>
+    <row r="37" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C37" s="10"/>
       <c r="D37" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
+        <v>259</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>192</v>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>263</v>
       </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="F38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C39" s="9"/>
+    <row r="39" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="D39" s="3" t="s">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="3" t="s">
-        <v>202</v>
+    <row r="40" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>273</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="J40" s="32" t="s">
-        <v>205</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C41" s="9"/>
+    <row r="41" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>212</v>
+        <v>278</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>279</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C42" s="9"/>
+    <row r="42" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>218</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>219</v>
+    <row r="43" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>284</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
-        <v>221</v>
+        <v>285</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3" t="s">
-        <v>223</v>
-      </c>
+    <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C44" s="10"/>
       <c r="D44" s="3" t="s">
-        <v>224</v>
+        <v>291</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="I44" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="J44" s="34" t="s">
+        <v>294</v>
+      </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C45" s="9"/>
+    <row r="45" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="10"/>
       <c r="D45" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>88</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J45" s="23" t="s">
-        <v>230</v>
-      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C46" s="9"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="23"/>
+    <row r="46" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="19" t="s">
-        <v>234</v>
-      </c>
+    <row r="47" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="10"/>
       <c r="D47" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>116</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="K47" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="L47" s="24"/>
-      <c r="M47" s="24"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
-        <v>240</v>
+    <row r="48" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="B48" s="3"/>
-      <c r="C48" s="19" t="s">
-        <v>241</v>
+      <c r="C48" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>116</v>
+        <v>307</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49" s="9"/>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C49" s="10"/>
       <c r="D49" s="3" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I49" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>249</v>
+        <v>94</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C50" s="9"/>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="D50" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>254</v>
+        <v>164</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>256</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="26"/>
+    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="D51" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>260</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
     </row>
-    <row r="52" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B52" t="s">
-        <v>262</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>263</v>
+    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" s="10"/>
+      <c r="D52" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H52" t="s">
-        <v>265</v>
-      </c>
-      <c r="I52" t="s">
-        <v>266</v>
-      </c>
-      <c r="J52" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-    </row>
-    <row r="57" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="28"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
+        <v>324</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="4"/>
+    </row>
+    <row r="54" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J55" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="K55" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I57" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="10"/>
+      <c r="D58" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="28"/>
+      <c r="D59" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B60" t="s">
+        <v>360</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="H60" t="s">
+        <v>363</v>
+      </c>
+      <c r="I60" t="s">
+        <v>364</v>
+      </c>
+      <c r="J60" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+    </row>
+    <row r="66" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="N52" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
+    <hyperlink ref="N24" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
+    <hyperlink ref="N21" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4994,60 +5412,60 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="41.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>269</v>
+        <v>367</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>270</v>
+        <v>368</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>272</v>
+        <v>370</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5059,12 +5477,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5076,31 +5494,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5114,70 +5532,70 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="60.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="C4" s="13" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
+      <c r="D5" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
       <c r="B6" s="3" t="s">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>289</v>
+        <v>384</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>385</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5185,39 +5603,39 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="22"/>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E9" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5228,17 +5646,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5445,6 +5852,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5455,17 +5873,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5484,6 +5891,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
   <ds:schemaRefs>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/eduard_derijcke_nictiz_nl/Documents/Bureaublad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Nictiz\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8B207D1-1355-40B1-8598-1BBE603C0CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD10C5A-4E46-4677-812B-8C2FB5410E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -63,7 +63,6 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={FC56F738-FB65-495B-9B48-E0F47216F010}</author>
     <author>tc={B3533A99-0CB6-4646-9417-20A66FEFD573}</author>
     <author>tc={20B2A504-5F6F-4996-9921-E2104F9548D8}</author>
     <author>tc={DC3A08E9-01DD-48D1-B7F5-357810DE5428}</author>
@@ -72,15 +71,7 @@
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
-      <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
-    AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
-      </text>
-    </comment>
-    <comment ref="K21" authorId="1" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -90,7 +81,7 @@
 Kortere waardelijst</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="2" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+    <comment ref="K26" authorId="1" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -98,7 +89,7 @@
     Wel in metadata!</t>
       </text>
     </comment>
-    <comment ref="E30" authorId="3" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="E29" authorId="2" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -106,7 +97,7 @@
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B32" authorId="4" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B31" authorId="3" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -114,7 +105,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="5" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C31" authorId="4" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -122,7 +113,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C40" authorId="6" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C39" authorId="5" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
         <t>[Opmerkingenthread]
 U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="391">
   <si>
     <t>Veld</t>
   </si>
@@ -375,12 +366,6 @@
     <t>Opmerking</t>
   </si>
   <si>
-    <t>[Nummer van de informatie-requirement start bij 1, sub behoeftes kunnen worden gemodelleerd met X.X of X.X.X]</t>
-  </si>
-  <si>
-    <t>[Naam waaraan de informatie-requirement te herkennen is]</t>
-  </si>
-  <si>
     <t>[Geef hier een tekstuele omschrijving van de behoefte die ingevuld wordt met de informatie-requirement]</t>
   </si>
   <si>
@@ -388,9 +373,6 @@
   </si>
   <si>
     <t>[Geef aan in welke situaties het element waarmee de informatie-requirement gedekt wordt er zou moeten zijn, en evt. wanneer het afwezig kan zijn]</t>
-  </si>
-  <si>
-    <t>[Geef aan of de informatie relevant is voor gebruik van het model voor zaken in het verleden, in het heden, en/of de toekomst. Vaak is slechts een van deze situaties in scope van het bouwblok, maar niet altijd]</t>
   </si>
   <si>
     <t>[Geef aan waar de behoefte vandaan komt, bv. een specifieke informatiestandaard of bepaalde zorgrichtlijn]</t>
@@ -1592,7 +1574,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1615,13 +1597,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1812,20 +1787,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1840,27 +1815,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1869,53 +1843,53 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2863,8 +2837,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N60" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:N60" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:N59" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
@@ -3234,27 +3208,24 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
-    <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
-  </threadedComment>
-  <threadedComment ref="K21" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+  <threadedComment ref="K20" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
     <text>1. Actief
 2. Inactief
 Kortere waardelijst</text>
   </threadedComment>
-  <threadedComment ref="K27" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+  <threadedComment ref="K26" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
     <text>Wel in metadata!</text>
   </threadedComment>
-  <threadedComment ref="E30" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+  <threadedComment ref="E29" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
   </threadedComment>
-  <threadedComment ref="B32" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+  <threadedComment ref="B31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C32" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+  <threadedComment ref="C31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C40" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C39" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
   </threadedComment>
 </ThreadedComments>
@@ -3424,7 +3395,7 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3682,7 +3653,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -3745,80 +3716,84 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="J3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="3" t="s">
+      <c r="L3" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="19"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="C4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="D4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="N4" s="20"/>
-      <c r="O4" s="9"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="E4" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="F4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3827,26 +3802,26 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>95</v>
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3855,26 +3830,26 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3883,27 +3858,20 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="B8" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="8"/>
       <c r="D8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3911,332 +3879,332 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="C9" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="8"/>
       <c r="D9" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>110</v>
-      </c>
+    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
-        <v>119</v>
-      </c>
+    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="L11" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="10"/>
+    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>128</v>
+        <v>134</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>131</v>
+    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>139</v>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>143</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>146</v>
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>151</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="3" t="s">
         <v>155</v>
       </c>
+      <c r="B16" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>116</v>
-      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="D17" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>160</v>
+    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>164</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>116</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
-        <v>168</v>
-      </c>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -4244,309 +4212,319 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="E20" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>175</v>
+      <c r="N20" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>180</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>178</v>
+        <v>181</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>181</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="B22" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="C22" s="10"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>138</v>
-      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="23"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="36"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="D23" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="F23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="H23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="L23" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="24" t="s">
-        <v>190</v>
+      <c r="C24" s="23" t="s">
+        <v>197</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L24" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="I24" s="38"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C25" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="37" t="s">
         <v>202</v>
       </c>
+      <c r="E25" s="37" t="s">
+        <v>203</v>
+      </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="24"/>
+        <v>204</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="23"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="40"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="5"/>
-    </row>
-    <row r="26" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="38" t="s">
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="B26" s="10" t="s">
         <v>206</v>
       </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="3" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="B27" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="C28" s="23"/>
-      <c r="F28" s="3"/>
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="H28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>219</v>
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>220</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>223</v>
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>224</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -4555,26 +4533,26 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>227</v>
+    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -4583,65 +4561,60 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
-        <v>233</v>
-      </c>
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="10"/>
       <c r="D32" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C33" s="10"/>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="D33" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="K33" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
+      <c r="E33" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>244</v>
       </c>
       <c r="B34" s="3"/>
@@ -4652,148 +4625,153 @@
         <v>246</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>163</v>
+        <v>247</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>247</v>
+    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="32"/>
+      <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3" t="s">
-        <v>253</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="10"/>
       <c r="D36" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C37" s="10"/>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J37" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K37" s="3"/>
+      <c r="E37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>263</v>
+    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>264</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>266</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>267</v>
+    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>268</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="C39" s="34" t="s">
         <v>269</v>
       </c>
+      <c r="D39" s="17" t="s">
+        <v>270</v>
+      </c>
       <c r="E39" s="3" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -4802,217 +4780,217 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="35" t="s">
+    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="B40" s="10" t="s">
         <v>273</v>
       </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E40" s="3" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>276</v>
+      </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>276</v>
-      </c>
+    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B41" s="3"/>
       <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>192</v>
+        <v>279</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>94</v>
+        <v>280</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J41" s="21" t="s">
-        <v>279</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J42" s="3"/>
+        <v>284</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B43" s="3"/>
+    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>287</v>
+      </c>
       <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3" t="s">
-        <v>288</v>
+        <v>91</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>291</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>290</v>
-      </c>
+    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="B44" s="3"/>
       <c r="C44" s="10"/>
       <c r="D44" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E44" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I44" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="J44" s="34" t="s">
-        <v>294</v>
-      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="3"/>
+    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>294</v>
+      </c>
       <c r="C45" s="10"/>
       <c r="D45" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
+      <c r="E45" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>297</v>
-      </c>
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B46" s="3"/>
       <c r="C46" s="10"/>
       <c r="D46" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I46" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="10"/>
       <c r="D47" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="E47" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -5020,68 +4998,65 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
         <v>306</v>
       </c>
+      <c r="B48" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C48" s="10"/>
       <c r="D48" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1</v>
+        <v>309</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C49" s="10"/>
+      <c r="A49" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="D49" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>314</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="20" t="s">
+    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
         <v>315</v>
       </c>
       <c r="B50" s="3"/>
@@ -5092,11 +5067,11 @@
         <v>317</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -5106,298 +5081,273 @@
       <c r="N50" s="3"/>
     </row>
     <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3" t="s">
+      <c r="B51" s="10" t="s">
         <v>319</v>
       </c>
+      <c r="C51" s="10"/>
       <c r="D51" s="3" t="s">
         <v>320</v>
       </c>
+      <c r="E51" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="F51" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="K51" s="4"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+      <c r="N51" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>322</v>
-      </c>
+      <c r="A52" s="9"/>
+      <c r="B52" s="3"/>
       <c r="C52" s="10"/>
       <c r="D52" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>326</v>
-      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="24"/>
       <c r="K52" s="4"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
-      <c r="N52" s="4" t="s">
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="3"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="25"/>
-      <c r="K53" s="4"/>
+      <c r="J53" s="23"/>
+      <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
-      <c r="N53" s="4"/>
-    </row>
-    <row r="54" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="D54" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="F54" s="3"/>
+      <c r="E54" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
+      <c r="H54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="K54" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
       <c r="N54" s="3"/>
     </row>
-    <row r="55" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="B55" s="10"/>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="J55" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="K55" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
+        <v>248</v>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
       <c r="N55" s="3"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3" t="s">
+    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
         <v>339</v>
       </c>
+      <c r="B56" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C56" s="10"/>
       <c r="D56" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
-        <v>342</v>
+    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="19" t="s">
+        <v>345</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>113</v>
+        <v>349</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I57" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="J57" s="21" t="s">
-        <v>347</v>
+        <v>91</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="C58" s="10"/>
+    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="27"/>
       <c r="D58" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>352</v>
+        <v>161</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="3" t="s">
+    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>356</v>
       </c>
+      <c r="B59" t="s">
+        <v>357</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>358</v>
+      </c>
       <c r="E59" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B60" t="s">
+      <c r="H59" t="s">
         <v>360</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="I59" t="s">
         <v>361</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="J59" t="s">
         <v>362</v>
       </c>
-      <c r="H60" t="s">
-        <v>363</v>
-      </c>
-      <c r="I60" t="s">
-        <v>364</v>
-      </c>
-      <c r="J60" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+    </row>
+    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-    </row>
-    <row r="65" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
-    </row>
-    <row r="66" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="C64" s="30"/>
+    </row>
+    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N52" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
-    <hyperlink ref="N24" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
-    <hyperlink ref="N21" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
+    <hyperlink ref="N51" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
+    <hyperlink ref="N23" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
+    <hyperlink ref="N20" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -5424,10 +5374,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>64</v>
@@ -5447,25 +5397,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5482,7 +5432,7 @@
     <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5502,7 +5452,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>34</v>
@@ -5510,15 +5460,15 @@
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5542,7 +5492,7 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -5550,52 +5500,52 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>56</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>382</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>385</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5605,37 +5555,37 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>384</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>387</v>
       </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="36" t="s">
-        <v>389</v>
+      <c r="D8" s="35" t="s">
+        <v>386</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="E9" s="24"/>
+        <v>389</v>
+      </c>
+      <c r="E9" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5646,6 +5596,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5852,17 +5813,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5873,6 +5823,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5891,23 +5858,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
   <ds:schemaRefs>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Nictiz\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahenket/Development/GitHub/Nictiz/GBB-IG/input/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD10C5A-4E46-4677-812B-8C2FB5410E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED832230-90A2-B141-8A59-508F66A307AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-140" yWindow="-26660" windowWidth="43920" windowHeight="26260" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -126,15 +126,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="390">
   <si>
     <t>Veld</t>
   </si>
   <si>
     <t>Beschrijving</t>
-  </si>
-  <si>
-    <t>a.d.h.v. keuze FHIR als basismodel</t>
   </si>
   <si>
     <t>Conceptbeschrijving</t>
@@ -1652,7 +1649,6 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1675,6 +1671,7 @@
       <sz val="9"/>
       <color rgb="FF4D4D4D"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1699,7 +1696,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1989,6 +1985,46 @@
       </border>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2054,46 +2090,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2815,44 +2811,44 @@
   <autoFilter ref="A2:C13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Uitleg" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="Beschrijving"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="A2:N59" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="18"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="16"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
     <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="14"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3234,15 +3230,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="218.42578125" customWidth="1"/>
+    <col min="1" max="1" width="218.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3251,7 +3247,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3269,138 +3265,138 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="46.7109375" customWidth="1"/>
-    <col min="3" max="3" width="59.7109375" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" customWidth="1"/>
+    <col min="3" max="3" width="59.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="190.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="219.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="165" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="408" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="156" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="256" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="349.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7"/>
     </row>
@@ -3420,214 +3416,214 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="51.28515625" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" customWidth="1"/>
+    <col min="5" max="5" width="58.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3654,74 +3650,74 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
-    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="87.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="78" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" customWidth="1"/>
-    <col min="9" max="9" width="28.140625" customWidth="1"/>
-    <col min="10" max="10" width="51.28515625" customWidth="1"/>
-    <col min="11" max="11" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="38.5703125" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="32.5" customWidth="1"/>
+    <col min="9" max="9" width="28.1640625" customWidth="1"/>
+    <col min="10" max="10" width="51.33203125" customWidth="1"/>
+    <col min="11" max="11" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="38.5" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>82</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="19"/>
@@ -3730,42 +3726,42 @@
       <c r="G3" s="19"/>
       <c r="H3" s="19"/>
       <c r="I3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="L3" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N3" s="19"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -3774,26 +3770,26 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3802,26 +3798,26 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -3830,26 +3826,26 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="E7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -3858,16 +3854,16 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>105</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -3879,244 +3875,244 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="K11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="E15" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>155</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>156</v>
       </c>
       <c r="C16" s="3"/>
       <c r="F16" s="3"/>
@@ -4129,60 +4125,60 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="J17" s="32" t="s">
-        <v>163</v>
-      </c>
       <c r="K17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -4191,16 +4187,16 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>169</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>170</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -4212,81 +4208,81 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>175</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="K20" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="C21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="C22" s="10"/>
       <c r="F22" s="3"/>
@@ -4299,66 +4295,66 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="K23" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="L23" s="36" t="s">
+      <c r="M23" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="N23" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N23" s="5" t="s">
+    </row>
+    <row r="24" spans="1:14" ht="80" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I24" s="38"/>
       <c r="J24" s="23"/>
@@ -4367,26 +4363,26 @@
       <c r="M24" s="3"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="E25" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="37" t="s">
-        <v>203</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="23"/>
@@ -4395,108 +4391,108 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="K26" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>211</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>212</v>
       </c>
       <c r="C27" s="22"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -4505,26 +4501,26 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -4533,26 +4529,26 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="F31" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -4561,78 +4557,78 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="E33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="31"/>
@@ -4641,26 +4637,26 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="F35" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -4669,81 +4665,81 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E37" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -4752,26 +4748,26 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>270</v>
-      </c>
       <c r="E39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -4780,59 +4776,59 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J40" s="20" t="s">
         <v>275</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>276</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -4840,72 +4836,72 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>287</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I43" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="J43" s="33" t="s">
         <v>290</v>
-      </c>
-      <c r="J43" s="33" t="s">
-        <v>291</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="3"/>
       <c r="C44" s="10"/>
       <c r="D44" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4917,48 +4913,48 @@
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="10"/>
       <c r="D46" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -4970,26 +4966,26 @@
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -4998,55 +4994,55 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I48" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -5055,23 +5051,23 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>317</v>
-      </c>
       <c r="F50" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -5080,46 +5076,46 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>318</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>319</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I51" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J51" s="24" t="s">
         <v>322</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>323</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="3"/>
       <c r="C52" s="10"/>
       <c r="D52" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -5131,12 +5127,12 @@
       <c r="M52" s="3"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>326</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="C53" s="10"/>
       <c r="F53" s="3"/>
@@ -5149,60 +5145,60 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
     </row>
-    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I54" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J54" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="J54" s="20" t="s">
+      <c r="K54" s="25" t="s">
         <v>333</v>
-      </c>
-      <c r="K54" s="25" t="s">
-        <v>334</v>
       </c>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
       <c r="N54" s="3"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
@@ -5211,134 +5207,134 @@
       <c r="M55" s="17"/>
       <c r="N55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>339</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>340</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I56" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="J56" s="20" t="s">
         <v>343</v>
-      </c>
-      <c r="J56" s="20" t="s">
-        <v>344</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I57" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s">
         <v>356</v>
       </c>
-      <c r="B59" t="s">
+      <c r="D59" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="E59" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="H59" t="s">
         <v>359</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>360</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>361</v>
       </c>
-      <c r="J59" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B63" s="28"/>
       <c r="C63" s="28"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
     </row>
-    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
     </row>
@@ -5362,60 +5358,60 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5427,12 +5423,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -5444,31 +5440,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.5" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5482,70 +5478,70 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="60.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="E3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="14" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>380</v>
-      </c>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19"/>
       <c r="B6" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>381</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>382</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5553,37 +5549,37 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B7" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="B8" s="14" t="s">
         <v>384</v>
-      </c>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>385</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>388</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>389</v>
       </c>
       <c r="E9" s="23"/>
     </row>
@@ -5607,6 +5603,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5813,15 +5818,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>
@@ -5840,6 +5836,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5856,12 +5860,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>